--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_repMonster.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_repMonster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_repMonster" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="1370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="1370">
   <si>
     <t>唯一id</t>
   </si>
@@ -618,1267 +618,1267 @@
     <t>15001001#3#83#33#1|15001001#3#120#69#1|15001001#3#158#31#1|15001001#3#80#30#1|15001001#3#118#72#1|15001001#3#161#35#1|15001001#3#81#35#1|15001001#3#124#72#1|15001001#3#162#29#1|15001001#3#75#29#1|15001001#3#117#75#1|15001001#3#164#36#1|15001001#3#76#35#1|15001001#3#122#75#1|15001001#3#164#29#1|15001002#2#83#33#1|15001002#2#120#69#1|15001002#2#158#31#1|15001002#2#80#30#1|15001002#2#118#72#1|15001002#2#161#35#1|15001002#2#81#35#1|15001002#2#124#72#1|15001002#2#162#29#1|15001002#2#75#29#1|15001002#2#117#75#1|15001002#2#164#36#1|15001002#2#76#35#1|15001002#2#122#75#1|15001002#2#164#29#1|15001003#1#83#33#1|15001003#1#120#69#1|15001003#1#158#31#1|15001003#1#80#30#1|15001003#1#118#72#1|15001003#1#161#35#1|15001003#1#81#35#1|15001003#1#124#72#1|15001003#1#162#29#1|15001003#1#75#29#1|15001003#1#117#75#1|15001003#1#164#36#1|15001003#1#76#35#1|15001003#1#122#75#1|15001003#1#164#29#1</t>
   </si>
   <si>
+    <t>狼魂要塞1副本-第2波</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第3波</t>
+  </si>
+  <si>
+    <t>15001004#3#83#33#1|15001004#3#120#69#1|15001004#3#158#31#1|15001004#3#80#30#1|15001004#3#118#72#1|15001004#3#161#35#1|15001004#3#81#35#1|15001004#3#124#72#1|15001004#3#162#29#1|15001004#3#75#29#1|15001004#3#117#75#1|15001004#3#164#36#1|15001004#3#76#35#1|15001004#3#122#75#1|15001005#2#83#33#1|15001005#2#120#69#1|15001005#2#158#31#1|15001005#2#80#30#1|15001005#2#118#72#1|15001005#2#161#35#1|15001005#2#81#35#1|15001005#2#124#72#1|15001005#2#162#29#1|15001005#2#75#29#1|15001005#2#117#75#1|15001005#2#164#36#1|15001005#2#76#35#1|15001005#2#122#75#1|15001006#1#83#33#1|15001006#1#120#69#1|15001006#1#158#31#1|15001006#1#80#30#1|15001006#1#118#72#1|15001006#1#161#35#1|15001006#1#81#35#1|15001006#1#124#72#1|15001006#1#162#29#1|15001006#1#75#29#1|15001006#1#117#75#1|15001006#1#164#36#1|15001006#1#76#35#1|15001006#1#122#75#1</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第4波</t>
+  </si>
+  <si>
+    <t>15001004#3#83#33#1|15001004#3#120#69#1|15001004#3#158#31#1|15001004#3#80#30#1|15001004#3#118#72#1|15001004#3#161#35#1|15001004#3#81#35#1|15001004#3#124#72#1|15001004#3#162#29#1|15001004#3#75#29#1|15001004#3#117#75#1|15001004#3#164#36#1|15001004#3#76#35#1|15001004#3#122#75#1|15001005#2#83#33#1|15001005#2#120#69#1|15001005#2#158#31#1|15001005#2#80#30#1|15001005#2#118#72#1|15001005#2#161#35#1|15001005#2#81#35#1|15001005#2#124#72#1|15001005#2#162#29#1|15001005#2#75#29#1|15001005#2#117#75#1|15001005#2#164#36#1|15001005#2#76#35#1|15001005#2#122#75#1|15001006#1#83#33#1|15001006#1#120#69#1|15001006#1#158#31#1|15001006#1#80#30#1|15001006#1#118#72#1|15001006#1#161#35#1|15001006#1#81#35#1|15001006#1#124#72#1|15001006#1#162#29#1|15001006#1#75#29#1|15001006#1#117#75#1|15001006#1#164#36#1|15001006#1#76#35#1|15001006#1#122#75#1|15001054#1#83#33#1|15001054#1#120#69#1|15001054#1#158#31#1</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第5波</t>
+  </si>
+  <si>
+    <t>15001007#3#83#33#1|15001007#3#120#69#1|15001007#3#158#31#1|15001007#3#80#30#1|15001007#3#118#72#1|15001007#3#161#35#1|15001007#3#81#35#1|15001007#3#124#72#1|15001007#3#162#29#1|15001007#3#75#29#1|15001007#3#117#75#1|15001007#3#164#36#1|15001007#3#76#35#1|15001008#2#83#33#1|15001008#2#120#69#1|15001008#2#158#31#1|15001008#2#80#30#1|15001008#2#118#72#1|15001008#2#161#35#1|15001008#2#81#35#1|15001008#2#124#72#1|15001008#2#162#29#1|15001008#2#75#29#1|15001008#2#117#75#1|15001008#2#164#36#1|15001008#2#76#35#1|15001009#1#83#33#1|15001009#1#120#69#1|15001009#1#158#31#1|15001009#1#80#30#1|15001009#1#118#72#1|15001009#1#161#35#1|15001009#1#81#35#1|15001009#1#124#72#1|15001009#1#162#29#1|15001009#1#75#29#1|15001009#1#117#75#1|15001009#1#164#36#1|15001009#1#76#35#1</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第6波</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第7波</t>
+  </si>
+  <si>
+    <t>15001010#3#83#33#1|15001010#3#120#69#1|15001010#3#158#31#1|15001010#3#80#30#1|15001010#3#118#72#1|15001010#3#161#35#1|15001010#3#81#35#1|15001010#3#124#72#1|15001010#3#162#29#1|15001010#3#75#29#1|15001010#3#117#75#1|15001010#3#164#36#1|15001011#2#83#33#1|15001011#2#120#69#1|15001011#2#158#31#1|15001011#2#80#30#1|15001011#2#118#72#1|15001011#2#161#35#1|15001011#2#81#35#1|15001011#2#124#72#1|15001011#2#162#29#1|15001011#2#75#29#1|15001011#2#117#75#1|15001011#2#164#36#1|15001012#1#83#33#1|15001012#1#120#69#1|15001012#1#158#31#1|15001012#1#80#30#1|15001012#1#118#72#1|15001012#1#161#35#1|15001012#1#81#35#1|15001012#1#124#72#1|15001012#1#162#29#1|15001012#1#75#29#1|15001012#1#117#75#1|15001012#1#164#36#1</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第8波</t>
+  </si>
+  <si>
+    <t>15001010#3#83#33#1|15001010#3#120#69#1|15001010#3#158#31#1|15001010#3#80#30#1|15001010#3#118#72#1|15001010#3#161#35#1|15001010#3#81#35#1|15001010#3#124#72#1|15001010#3#162#29#1|15001010#3#75#29#1|15001010#3#117#75#1|15001010#3#164#36#1|15001011#2#83#33#1|15001011#2#120#69#1|15001011#2#158#31#1|15001011#2#80#30#1|15001011#2#118#72#1|15001011#2#161#35#1|15001011#2#81#35#1|15001011#2#124#72#1|15001011#2#162#29#1|15001011#2#75#29#1|15001011#2#117#75#1|15001011#2#164#36#1|15001012#1#83#33#1|15001012#1#120#69#1|15001012#1#158#31#1|15001012#1#80#30#1|15001012#1#118#72#1|15001012#1#161#35#1|15001012#1#81#35#1|15001012#1#124#72#1|15001012#1#162#29#1|15001012#1#75#29#1|15001012#1#117#75#1|15001012#1#164#36#1|15001054#1#83#33#1|15001054#1#120#69#1|15001054#1#158#31#1</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第9波</t>
+  </si>
+  <si>
+    <t>15001013#3#83#33#1|15001013#3#120#69#1|15001013#3#158#31#1|15001013#3#80#30#1|15001013#3#118#72#1|15001013#3#161#35#1|15001013#3#81#35#1|15001013#3#124#72#1|15001013#3#162#29#1|15001013#3#75#29#1|15001013#3#117#75#1|15001014#2#83#33#1|15001014#2#120#69#1|15001014#2#158#31#1|15001014#2#80#30#1|15001014#2#118#72#1|15001014#2#161#35#1|15001014#2#81#35#1|15001014#2#124#72#1|15001014#2#162#29#1|15001014#2#75#29#1|15001014#2#117#75#1|15001015#1#83#33#1|15001015#1#120#69#1|15001015#1#158#31#1|15001015#1#80#30#1|15001015#1#118#72#1|15001015#1#161#35#1|15001015#1#81#35#1|15001015#1#124#72#1|15001015#1#162#29#1|15001015#1#75#29#1|15001015#1#117#75#1</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第10波</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第11波</t>
+  </si>
+  <si>
+    <t>15001016#3#83#33#1|15001016#3#120#69#1|15001016#3#158#31#1|15001016#3#80#30#1|15001016#3#118#72#1|15001016#3#161#35#1|15001016#3#81#35#1|15001016#3#124#72#1|15001016#3#162#29#1|15001016#3#75#29#1|15001017#2#83#33#1|15001017#2#120#69#1|15001017#2#158#31#1|15001017#2#80#30#1|15001017#2#118#72#1|15001017#2#161#35#1|15001017#2#81#35#1|15001017#2#124#72#1|15001017#2#162#29#1|15001017#2#75#29#1|15001018#1#83#33#1|15001018#1#120#69#1|15001018#1#158#31#1|15001018#1#80#30#1|15001018#1#118#72#1|15001018#1#161#35#1|15001018#1#81#35#1|15001018#1#124#72#1|15001018#1#162#29#1|15001018#1#75#29#1</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第12波</t>
+  </si>
+  <si>
+    <t>15001016#3#83#33#1|15001016#3#120#69#1|15001016#3#158#31#1|15001016#3#80#30#1|15001016#3#118#72#1|15001016#3#161#35#1|15001016#3#81#35#1|15001016#3#124#72#1|15001016#3#162#29#1|15001016#3#75#29#1|15001017#2#83#33#1|15001017#2#120#69#1|15001017#2#158#31#1|15001017#2#80#30#1|15001017#2#118#72#1|15001017#2#161#35#1|15001017#2#81#35#1|15001017#2#124#72#1|15001017#2#162#29#1|15001017#2#75#29#1|15001018#1#83#33#1|15001018#1#120#69#1|15001018#1#158#31#1|15001018#1#80#30#1|15001018#1#118#72#1|15001018#1#161#35#1|15001018#1#81#35#1|15001018#1#124#72#1|15001018#1#162#29#1|15001018#1#75#29#1|15001054#1#83#33#1|15001054#1#120#69#1|15001054#1#158#31#1</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第13波</t>
+  </si>
+  <si>
+    <t>15001019#3#83#33#1|15001019#3#120#69#1|15001019#3#158#31#1|15001019#3#80#30#1|15001019#3#118#72#1|15001019#3#161#35#1|15001019#3#81#35#1|15001019#3#124#72#1|15001019#3#162#29#1|15001020#2#83#33#1|15001020#2#120#69#1|15001020#2#158#31#1|15001020#2#80#30#1|15001020#2#118#72#1|15001020#2#161#35#1|15001020#2#81#35#1|15001020#2#124#72#1|15001020#2#162#29#1|15001021#1#83#33#1|15001021#1#120#69#1|15001021#1#158#31#1|15001021#1#80#30#1|15001021#1#118#72#1|15001021#1#161#35#1|15001021#1#81#35#1|15001021#1#124#72#1|15001021#1#162#29#1</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第14波</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第15波</t>
+  </si>
+  <si>
+    <t>15001022#3#83#33#1|15001022#3#120#69#1|15001022#3#158#31#1|15001022#3#80#30#1|15001022#3#118#72#1|15001022#3#161#35#1|15001022#3#81#35#1|15001022#3#124#72#1|15001022#3#162#29#1|15001023#2#83#33#1|15001023#2#120#69#1|15001023#2#158#31#1|15001023#2#80#30#1|15001023#2#118#72#1|15001023#2#161#35#1|15001023#2#81#35#1|15001023#2#124#72#1|15001023#2#162#29#1|15001024#1#83#33#1|15001024#1#120#69#1|15001024#1#158#31#1|15001024#1#80#30#1|15001024#1#118#72#1|15001024#1#161#35#1|15001024#1#81#35#1|15001024#1#124#72#1|15001024#1#162#29#1</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第16波</t>
+  </si>
+  <si>
+    <t>15001022#3#83#33#1|15001022#3#120#69#1|15001022#3#158#31#1|15001022#3#80#30#1|15001022#3#118#72#1|15001022#3#161#35#1|15001022#3#81#35#1|15001022#3#124#72#1|15001022#3#162#29#1|15001023#2#83#33#1|15001023#2#120#69#1|15001023#2#158#31#1|15001023#2#80#30#1|15001023#2#118#72#1|15001023#2#161#35#1|15001023#2#81#35#1|15001023#2#124#72#1|15001023#2#162#29#1|15001024#1#83#33#1|15001024#1#120#69#1|15001024#1#158#31#1|15001024#1#80#30#1|15001024#1#118#72#1|15001024#1#161#35#1|15001024#1#81#35#1|15001024#1#124#72#1|15001024#1#162#29#1|15001054#1#83#33#1|15001054#1#120#69#1|15001054#1#158#31#1</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第17波</t>
+  </si>
+  <si>
+    <t>15001025#3#83#33#1|15001025#3#120#69#1|15001025#3#158#31#1|15001025#3#80#30#1|15001025#3#118#72#1|15001025#3#161#35#1|15001025#3#81#35#1|15001025#3#124#72#1|15001025#3#162#29#1|15001026#2#83#33#1|15001026#2#120#69#1|15001026#2#158#31#1|15001026#2#80#30#1|15001026#2#118#72#1|15001026#2#161#35#1|15001026#2#81#35#1|15001026#2#124#72#1|15001026#2#162#29#1|15001027#1#83#33#1|15001027#1#120#69#1|15001027#1#158#31#1|15001027#1#80#30#1|15001027#1#118#72#1|15001027#1#161#35#1|15001027#1#81#35#1|15001027#1#124#72#1|15001027#1#162#29#1</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第18波</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第19波</t>
+  </si>
+  <si>
+    <t>15001028#3#83#33#1|15001028#3#120#69#1|15001028#3#158#31#1|15001028#3#80#30#1|15001028#3#118#72#1|15001028#3#161#35#1|15001028#3#81#35#1|15001028#3#124#72#1|15001028#3#162#29#1|15001029#2#83#33#1|15001029#2#120#69#1|15001029#2#158#31#1|15001029#2#80#30#1|15001029#2#118#72#1|15001029#2#161#35#1|15001029#2#81#35#1|15001029#2#124#72#1|15001029#2#162#29#1|15001030#1#83#33#1|15001030#1#120#69#1|15001030#1#158#31#1|15001030#1#80#30#1|15001030#1#118#72#1|15001030#1#161#35#1|15001030#1#81#35#1|15001030#1#124#72#1|15001030#1#162#29#1</t>
+  </si>
+  <si>
+    <t>狼魂要塞1副本-第20波</t>
+  </si>
+  <si>
+    <t>15001028#3#83#33#1|15001028#3#120#69#1|15001028#3#158#31#1|15001028#3#80#30#1|15001028#3#118#72#1|15001028#3#161#35#1|15001028#3#81#35#1|15001028#3#124#72#1|15001028#3#162#29#1|15001029#2#83#33#1|15001029#2#120#69#1|15001029#2#158#31#1|15001029#2#80#30#1|15001029#2#118#72#1|15001029#2#161#35#1|15001029#2#81#35#1|15001029#2#124#72#1|15001029#2#162#29#1|15001030#1#83#33#1|15001030#1#120#69#1|15001030#1#158#31#1|15001030#1#80#30#1|15001030#1#118#72#1|15001030#1#161#35#1|15001030#1#81#35#1|15001030#1#124#72#1|15001030#1#162#29#1|15001055#1#83#33#1|15001055#1#120#69#1</t>
+  </si>
+  <si>
+    <t>卡利玛神庙第1关</t>
+  </si>
+  <si>
+    <t>102500009#1#40#97#2|102500001#10#57#24#5|102500001#10#81#21#5|102500002#10#100#18#5|102500002#10#110#38#5|102500003#10#115#58#5|102500003#10#113#77#5|102500004#10#102#99#5|102500006#10#35#58#5|102500007#10#36#79#5</t>
+  </si>
+  <si>
+    <t>卡利玛神庙第2关</t>
+  </si>
+  <si>
+    <t>102500019#1#40#97#2|102500011#10#57#24#5|102500011#10#81#21#5|102500012#10#100#18#5|102500012#10#110#38#5|102500013#10#115#58#5|102500013#10#113#77#5|102500014#10#102#99#5|102500016#10#35#58#5|102500017#10#36#79#5</t>
+  </si>
+  <si>
+    <t>卡利玛神庙第3关</t>
+  </si>
+  <si>
+    <t>102500029#1#40#97#2|102500021#10#57#24#5|102500021#10#81#21#5|102500022#10#100#18#5|102500022#10#110#38#5|102500023#10#115#58#5|102500023#10#113#77#5|102500024#10#102#99#5|102500026#10#35#58#5|102500027#10#36#79#5</t>
+  </si>
+  <si>
+    <t>卡利玛神庙第4关</t>
+  </si>
+  <si>
+    <t>102500039#1#40#97#2|102500031#10#57#24#5|102500031#10#81#21#5|102500032#10#100#18#5|102500032#10#110#38#5|102500033#10#115#58#5|102500033#10#113#77#5|102500034#10#102#99#5|102500036#10#35#58#5|102500037#10#36#79#5</t>
+  </si>
+  <si>
+    <t>卡利玛神庙第5关</t>
+  </si>
+  <si>
+    <t>102500049#1#40#97#2|102500041#10#57#24#5|102500041#10#81#21#5|102500042#10#100#18#5|102500042#10#110#38#5|102500043#10#115#58#5|102500043#10#113#77#5|102500044#10#102#99#5|102500046#10#35#58#5|102500047#10#36#79#5</t>
+  </si>
+  <si>
+    <t>卡利玛神庙第6关</t>
+  </si>
+  <si>
+    <t>102500059#1#40#97#2|102500051#10#57#24#5|102500051#10#81#21#5|102500052#10#100#18#5|102500052#10#110#38#5|102500053#10#115#58#5|102500053#10#113#77#5|102500054#10#102#99#5|102500056#10#35#58#5|102500057#10#36#79#5</t>
+  </si>
+  <si>
+    <t>卡利玛神庙第7关</t>
+  </si>
+  <si>
+    <t>102500069#1#40#97#2|102500061#10#57#24#5|102500061#10#81#21#5|102500062#10#100#18#5|102500062#10#110#38#5|102500063#10#115#58#5|102500063#10#113#77#5|102500064#10#102#99#5|102500066#10#35#58#5|102500067#10#36#79#5</t>
+  </si>
+  <si>
+    <t>50005#20#127#104#10|50003#20#127#88#10|50005#20#142#88#10|50003#20#142#104#10|50006#20#137#92#10</t>
+  </si>
+  <si>
+    <t>50003#20#127#104#10|50006#20#127#88#10|50010#20#142#88#10|50003#20#142#104#10|50006#20#137#92#10</t>
+  </si>
+  <si>
+    <t>50003#20#127#104#10|50003#20#127#88#10|50005#20#142#88#10|50003#20#142#104#10|50006#20#137#92#10</t>
+  </si>
+  <si>
+    <t>50008#20#127#104#10|50009#20#127#88#10|50009#20#142#88#10|50008#20#142#104#10|50009#20#137#92#10</t>
+  </si>
+  <si>
+    <t>60001#20#127#104#10|60002#20#127#88#10|60003#20#142#88#10|60001#20#142#104#10|60002#20#137#92#10</t>
+  </si>
+  <si>
+    <t>60002#20#127#104#10|60003#20#127#88#10|60004#20#142#88#10|60002#20#142#104#10|60003#20#137#92#10</t>
+  </si>
+  <si>
+    <t>60004#20#127#104#10|60005#20#127#88#10|60006#20#142#88#10|60004#20#142#104#10|60005#20#137#92#10</t>
+  </si>
+  <si>
+    <t>60006#20#127#104#10|60007#20#127#88#10|60007#20#142#88#10|60005#20#142#104#10|60006#20#137#92#10</t>
+  </si>
+  <si>
+    <t>70001#20#127#104#10|70002#20#127#88#10|70003#20#142#88#10|70001#20#142#104#10|70002#20#137#92#10</t>
+  </si>
+  <si>
+    <t>70002#20#127#104#10|70003#20#127#88#10|70004#20#142#88#10|70002#20#142#104#10|70003#20#137#92#10</t>
+  </si>
+  <si>
+    <t>70003#20#127#104#10|70004#20#127#88#10|70005#20#142#88#10|70003#20#142#104#10|70004#20#137#92#10</t>
+  </si>
+  <si>
+    <t>70004#20#127#104#10|70005#20#127#88#10|70006#20#142#88#10|70004#20#142#104#10|70005#20#137#92#10</t>
+  </si>
+  <si>
+    <t>22001#20#127#104#10|22002#20#127#88#10|24004#20#142#88#10|22001#20#142#104#10|22002#20#137#92#10</t>
+  </si>
+  <si>
+    <t>22002#20#127#104#10|24004#20#127#88#10|24003#20#142#88#10|22002#20#142#104#10|24004#20#137#92#10</t>
+  </si>
+  <si>
+    <t>24003#20#127#104#10|80005#20#127#88#10|90003#20#142#88#10|24003#20#142#104#10|80005#20#137#92#10</t>
+  </si>
+  <si>
+    <t>80001#20#127#104#10|80002#20#127#88#10|80003#20#142#88#10|80001#20#142#104#10|80002#20#137#92#10</t>
+  </si>
+  <si>
+    <t>80002#20#127#104#10|80003#20#127#88#10|80004#20#142#88#10|80002#20#142#104#10|80003#20#137#92#10</t>
+  </si>
+  <si>
+    <t>80003#20#127#104#10|80004#20#127#88#10|80005#20#142#88#10|80003#20#142#104#10|80004#20#137#92#10</t>
+  </si>
+  <si>
+    <t>24005#20#127#104#10|24006#20#127#88#10|24007#20#142#88#10|24005#20#142#104#10|24006#20#137#92#10</t>
+  </si>
+  <si>
+    <t>90002#20#127#104#10|90001#20#127#88#10|90004#20#142#88#10|90002#20#142#104#10|90001#20#137#92#10</t>
+  </si>
+  <si>
+    <t>90001#20#127#104#10|90004#20#127#88#10|90005#20#142#88#10|90001#20#142#104#10|90005#20#137#92#10</t>
+  </si>
+  <si>
+    <t>90004#20#127#104#10|90005#20#127#88#10|90006#20#142#88#10|90004#20#142#104#10|90005#20#137#92#10</t>
+  </si>
+  <si>
+    <t>12006#20#127#104#10|12007#20#127#88#10|90006#20#142#88#10|90004#20#142#104#10|90005#20#137#92#10</t>
+  </si>
+  <si>
+    <t>12007#20#127#104#10|13001#20#127#88#10|13002#20#142#88#10|13001#20#142#104#10|13002#20#137#92#10</t>
+  </si>
+  <si>
+    <t>13001#20#127#104#10|13002#20#127#88#10|13003#20#142#88#10|13001#20#142#104#10|13002#20#137#92#10</t>
+  </si>
+  <si>
+    <t>恶魔广场8层1波</t>
+  </si>
+  <si>
+    <t>10008001#11#144#107#10|10008001#11#144#89#10|10008001#11#135#98#10|10008001#11#126#107#10|10008001#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场8层2波</t>
+  </si>
+  <si>
+    <t>10008002#11#144#107#10|10008002#11#144#89#10|10008002#11#135#98#10|10008002#11#126#107#10|10008002#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场8层3波</t>
+  </si>
+  <si>
+    <t>10008003#11#144#107#10|10008003#11#144#89#10|10008003#11#135#98#10|10008003#11#126#107#10|10008003#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场8层4波</t>
+  </si>
+  <si>
+    <t>10008004#11#144#107#10|10008004#11#144#89#10|10008004#11#135#98#10|10008004#11#126#107#10|10008004#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场9层1波</t>
+  </si>
+  <si>
+    <t>10009001#11#144#107#10|10009001#11#144#89#10|10009001#11#135#98#10|10009001#11#126#107#10|10009001#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场9层2波</t>
+  </si>
+  <si>
+    <t>10009002#11#144#107#10|10009002#11#144#89#10|10009002#11#135#98#10|10009002#11#126#107#10|10009002#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场9层3波</t>
+  </si>
+  <si>
+    <t>10009003#11#144#107#10|10009003#11#144#89#10|10009003#11#135#98#10|10009003#11#126#107#10|10009003#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场9层4波</t>
+  </si>
+  <si>
+    <t>10009004#11#144#107#10|10009004#11#144#89#10|10009004#11#135#98#10|10009004#11#126#107#10|10009004#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场10层1波</t>
+  </si>
+  <si>
+    <t>10010001#11#144#107#10|10010001#11#144#89#10|10010001#11#135#98#10|10010001#11#126#107#10|10010001#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场10层2波</t>
+  </si>
+  <si>
+    <t>10010002#11#144#107#10|10010002#11#144#89#10|10010002#11#135#98#10|10010002#11#126#107#10|10010002#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场10层3波</t>
+  </si>
+  <si>
+    <t>10010003#11#144#107#10|10010003#11#144#89#10|10010003#11#135#98#10|10010003#11#126#107#10|10010003#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场10层4波</t>
+  </si>
+  <si>
+    <t>10010004#11#144#107#10|10010004#11#144#89#10|10010004#11#135#98#10|10010004#11#126#107#10|10010004#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场11层1波</t>
+  </si>
+  <si>
+    <t>10011001#11#144#107#10|10011001#11#144#89#10|10011001#11#135#98#10|10011001#11#126#107#10|10011001#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场11层2波</t>
+  </si>
+  <si>
+    <t>10011002#11#144#107#10|10011002#11#144#89#10|10011002#11#135#98#10|10011002#11#126#107#10|10011002#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场11层3波</t>
+  </si>
+  <si>
+    <t>10011003#11#144#107#10|10011003#11#144#89#10|10011003#11#135#98#10|10011003#11#126#107#10|10011003#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场11层4波</t>
+  </si>
+  <si>
+    <t>10011004#11#144#107#10|10011004#11#144#89#10|10011004#11#135#98#10|10011004#11#126#107#10|10011004#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场12层1波</t>
+  </si>
+  <si>
+    <t>10012001#11#144#107#10|10012001#11#144#89#10|10012001#11#135#98#10|10012001#11#126#107#10|10012001#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场12层2波</t>
+  </si>
+  <si>
+    <t>10012002#11#144#107#10|10012002#11#144#89#10|10012002#11#135#98#10|10012002#11#126#107#10|10012002#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场12层3波</t>
+  </si>
+  <si>
+    <t>10012003#11#144#107#10|10012003#11#144#89#10|10012003#11#135#98#10|10012003#11#126#107#10|10012003#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场12层4波</t>
+  </si>
+  <si>
+    <t>10012004#11#144#107#10|10012004#11#144#89#10|10012004#11#135#98#10|10012004#11#126#107#10|10012004#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场13层1波</t>
+  </si>
+  <si>
+    <t>10013001#11#144#107#10|10013001#11#144#89#10|10013001#11#135#98#10|10013001#11#126#107#10|10013001#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场13层2波</t>
+  </si>
+  <si>
+    <t>10013002#11#144#107#10|10013002#11#144#89#10|10013002#11#135#98#10|10013002#11#126#107#10|10013002#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场13层3波</t>
+  </si>
+  <si>
+    <t>10013003#11#144#107#10|10013003#11#144#89#10|10013003#11#135#98#10|10013003#11#126#107#10|10013003#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场13层4波</t>
+  </si>
+  <si>
+    <t>10013004#11#144#107#10|10013004#11#144#89#10|10013004#11#135#98#10|10013004#11#126#107#10|10013004#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场14层1波</t>
+  </si>
+  <si>
+    <t>10014001#11#144#107#10|10014001#11#144#89#10|10014001#11#135#98#10|10014001#11#126#107#10|10014001#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场14层2波</t>
+  </si>
+  <si>
+    <t>10014002#11#144#107#10|10014002#11#144#89#10|10014002#11#135#98#10|10014002#11#126#107#10|10014002#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场14层3波</t>
+  </si>
+  <si>
+    <t>10014003#11#144#107#10|10014003#11#144#89#10|10014003#11#135#98#10|10014003#11#126#107#10|10014003#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场14层4波</t>
+  </si>
+  <si>
+    <t>10014004#11#144#107#10|10014004#11#144#89#10|10014004#11#135#98#10|10014004#11#126#107#10|10014004#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场15层1波</t>
+  </si>
+  <si>
+    <t>10015001#11#144#107#10|10015001#11#144#89#10|10015001#11#135#98#10|10015001#11#126#107#10|10015001#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场15层2波</t>
+  </si>
+  <si>
+    <t>10015002#11#144#107#10|10015002#11#144#89#10|10015002#11#135#98#10|10015002#11#126#107#10|10015002#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场15层3波</t>
+  </si>
+  <si>
+    <t>10015003#11#144#107#10|10015003#11#144#89#10|10015003#11#135#98#10|10015003#11#126#107#10|10015003#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场15层4波</t>
+  </si>
+  <si>
+    <t>10015004#11#144#107#10|10015004#11#144#89#10|10015004#11#135#98#10|10015004#11#126#107#10|10015004#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场16层1波</t>
+  </si>
+  <si>
+    <t>10016001#11#144#107#10|10016001#11#144#89#10|10016001#11#135#98#10|10016001#11#126#107#10|10016001#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场16层2波</t>
+  </si>
+  <si>
+    <t>10016002#11#144#107#10|10016002#11#144#89#10|10016002#11#135#98#10|10016002#11#126#107#10|10016002#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场16层3波</t>
+  </si>
+  <si>
+    <t>10016003#11#144#107#10|10016003#11#144#89#10|10016003#11#135#98#10|10016003#11#126#107#10|10016003#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场16层4波</t>
+  </si>
+  <si>
+    <t>10016004#11#144#107#10|10016004#11#144#89#10|10016004#11#135#98#10|10016004#11#126#107#10|10016004#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场17层1波</t>
+  </si>
+  <si>
+    <t>10017001#11#144#107#10|10017001#11#144#89#10|10017001#11#135#98#10|10017001#11#126#107#10|10017001#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场17层2波</t>
+  </si>
+  <si>
+    <t>10017002#11#144#107#10|10017002#11#144#89#10|10017002#11#135#98#10|10017002#11#126#107#10|10017002#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场17层3波</t>
+  </si>
+  <si>
+    <t>10017003#11#144#107#10|10017003#11#144#89#10|10017003#11#135#98#10|10017003#11#126#107#10|10017003#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场17层4波</t>
+  </si>
+  <si>
+    <t>10017004#11#144#107#10|10017004#11#144#89#10|10017004#11#135#98#10|10017004#11#126#107#10|10017004#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场18层1波</t>
+  </si>
+  <si>
+    <t>10018001#11#144#107#10|10018001#11#144#89#10|10018001#11#135#98#10|10018001#11#126#107#10|10018001#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场18层2波</t>
+  </si>
+  <si>
+    <t>10018002#11#144#107#10|10018002#11#144#89#10|10018002#11#135#98#10|10018002#11#126#107#10|10018002#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场18层3波</t>
+  </si>
+  <si>
+    <t>10018003#11#144#107#10|10018003#11#144#89#10|10018003#11#135#98#10|10018003#11#126#107#10|10018003#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场18层4波</t>
+  </si>
+  <si>
+    <t>10018004#11#144#107#10|10018004#11#144#89#10|10018004#11#135#98#10|10018004#11#126#107#10|10018004#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场19层1波</t>
+  </si>
+  <si>
+    <t>10019001#11#144#107#10|10019001#11#144#89#10|10019001#11#135#98#10|10019001#11#126#107#10|10019001#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场19层2波</t>
+  </si>
+  <si>
+    <t>10019002#11#144#107#10|10019002#11#144#89#10|10019002#11#135#98#10|10019002#11#126#107#10|10019002#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场19层3波</t>
+  </si>
+  <si>
+    <t>10019003#11#144#107#10|10019003#11#144#89#10|10019003#11#135#98#10|10019003#11#126#107#10|10019003#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场19层4波</t>
+  </si>
+  <si>
+    <t>10019004#11#144#107#10|10019004#11#144#89#10|10019004#11#135#98#10|10019004#11#126#107#10|10019004#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场20层1波</t>
+  </si>
+  <si>
+    <t>10020001#11#144#107#10|10020001#11#144#89#10|10020001#11#135#98#10|10020001#11#126#107#10|10020001#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场20层2波</t>
+  </si>
+  <si>
+    <t>10020002#11#144#107#10|10020002#11#144#89#10|10020002#11#135#98#10|10020002#11#126#107#10|10020002#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场20层3波</t>
+  </si>
+  <si>
+    <t>10020003#11#144#107#10|10020003#11#144#89#10|10020003#11#135#98#10|10020003#11#126#107#10|10020003#11#123#90#10</t>
+  </si>
+  <si>
+    <t>恶魔广场20层4波</t>
+  </si>
+  <si>
+    <t>10020004#11#144#107#10|10020004#11#144#89#10|10020004#11#135#98#10|10020004#11#126#107#10|10020004#11#123#90#10</t>
+  </si>
+  <si>
+    <t>血色城堡1</t>
+  </si>
+  <si>
+    <t>血色城堡2</t>
+  </si>
+  <si>
+    <t>血色城堡3</t>
+  </si>
+  <si>
+    <t>血色城堡4</t>
+  </si>
+  <si>
+    <t>血色城堡5</t>
+  </si>
+  <si>
+    <t>血色城堡6</t>
+  </si>
+  <si>
+    <t>血色城堡7</t>
+  </si>
+  <si>
+    <t>血色城堡8</t>
+  </si>
+  <si>
+    <t>血色城堡9</t>
+  </si>
+  <si>
+    <t>血色城堡10</t>
+  </si>
+  <si>
+    <t>血色城堡11</t>
+  </si>
+  <si>
+    <t>11011001#8#14#21#3|11011002#8#14#24#3|11011003#8#14#27#3|11011004#8#14#31#3|11011001#8#14#34#3|11011002#8#14#37#3|11011003#8#14#41#3|11011004#8#14#44#3|11011001#8#14#47#3|11011002#8#14#51#3|11011003#8#14#54#3|11011004#8#14#57#3|11011001#8#14#59#3|11011002#8#14#61#3|11011003#8#14#64#3|11011005#5#14#85#5|11011005#5#21#82#5|11011005#5#22#88#5|11011006#5#14#85#5|11011006#5#21#82#5|11011006#5#22#88#5</t>
+  </si>
+  <si>
+    <t>血色城堡12</t>
+  </si>
+  <si>
+    <t>11012001#8#14#21#3|11012002#8#14#24#3|11012003#8#14#27#3|11012004#8#14#31#3|11012001#8#14#34#3|11012002#8#14#37#3|11012003#8#14#41#3|11012004#8#14#44#3|11012001#8#14#47#3|11012002#8#14#51#3|11012003#8#14#54#3|11012004#8#14#57#3|11012001#8#14#59#3|11012002#8#14#61#3|11012003#8#14#64#3|11012005#5#14#85#5|11012005#5#21#82#5|11012005#5#22#88#5|11012006#5#14#85#5|11012006#5#21#82#5|11012006#5#22#88#5</t>
+  </si>
+  <si>
+    <t>血色城堡13</t>
+  </si>
+  <si>
+    <t>11013001#8#14#21#3|11013002#8#14#24#3|11013003#8#14#27#3|11013004#8#14#31#3|11013001#8#14#34#3|11013002#8#14#37#3|11013003#8#14#41#3|11013004#8#14#44#3|11013001#8#14#47#3|11013002#8#14#51#3|11013003#8#14#54#3|11013004#8#14#57#3|11013001#8#14#59#3|11013002#8#14#61#3|11013003#8#14#64#3|11013005#5#14#85#5|11013005#5#21#82#5|11013005#5#22#88#5|11013006#5#14#85#5|11013006#5#21#82#5|11013006#5#22#88#5</t>
+  </si>
+  <si>
+    <t>血色城堡14</t>
+  </si>
+  <si>
+    <t>11014001#8#14#21#3|11014002#8#14#24#3|11014003#8#14#27#3|11014004#8#14#31#3|11014001#8#14#34#3|11014002#8#14#37#3|11014003#8#14#41#3|11014004#8#14#44#3|11014001#8#14#47#3|11014002#8#14#51#3|11014003#8#14#54#3|11014004#8#14#57#3|11014001#8#14#59#3|11014002#8#14#61#3|11014003#8#14#64#3|11014005#5#14#85#5|11014005#5#21#82#5|11014005#5#22#88#5|11014006#5#14#85#5|11014006#5#21#82#5|11014006#5#22#88#5</t>
+  </si>
+  <si>
+    <t>血色城堡15</t>
+  </si>
+  <si>
+    <t>11015001#8#14#21#3|11015002#8#14#24#3|11015003#8#14#27#3|11015004#8#14#31#3|11015001#8#14#34#3|11015002#8#14#37#3|11015003#8#14#41#3|11015004#8#14#44#3|11015001#8#14#47#3|11015002#8#14#51#3|11015003#8#14#54#3|11015004#8#14#57#3|11015001#8#14#59#3|11015002#8#14#61#3|11015003#8#14#64#3|11015005#5#14#85#5|11015005#5#21#82#5|11015005#5#22#88#5|11015006#5#14#85#5|11015006#5#21#82#5|11015006#5#22#88#5</t>
+  </si>
+  <si>
+    <t>血色城堡16</t>
+  </si>
+  <si>
+    <t>11016001#8#14#21#3|11016002#8#14#24#3|11016003#8#14#27#3|11016004#8#14#31#3|11016001#8#14#34#3|11016002#8#14#37#3|11016003#8#14#41#3|11016004#8#14#44#3|11016001#8#14#47#3|11016002#8#14#51#3|11016003#8#14#54#3|11016004#8#14#57#3|11016001#8#14#59#3|11016002#8#14#61#3|11016003#8#14#64#3|11016005#5#14#85#5|11016005#5#21#82#5|11016005#5#22#88#5|11016006#5#14#85#5|11016006#5#21#82#5|11016006#5#22#88#5</t>
+  </si>
+  <si>
+    <t>血色城堡17</t>
+  </si>
+  <si>
+    <t>11017001#8#14#21#3|11017002#8#14#24#3|11017003#8#14#27#3|11017004#8#14#31#3|11017001#8#14#34#3|11017002#8#14#37#3|11017003#8#14#41#3|11017004#8#14#44#3|11017001#8#14#47#3|11017002#8#14#51#3|11017003#8#14#54#3|11017004#8#14#57#3|11017001#8#14#59#3|11017002#8#14#61#3|11017003#8#14#64#3|11017005#5#14#85#5|11017005#5#21#82#5|11017005#5#22#88#5|11017006#5#14#85#5|11017006#5#21#82#5|11017006#5#22#88#5</t>
+  </si>
+  <si>
+    <t>血色城堡18</t>
+  </si>
+  <si>
+    <t>11018001#8#14#21#3|11018002#8#14#24#3|11018003#8#14#27#3|11018004#8#14#31#3|11018001#8#14#34#3|11018002#8#14#37#3|11018003#8#14#41#3|11018004#8#14#44#3|11018001#8#14#47#3|11018002#8#14#51#3|11018003#8#14#54#3|11018004#8#14#57#3|11018001#8#14#59#3|11018002#8#14#61#3|11018003#8#14#64#3|11018005#5#14#85#5|11018005#5#21#82#5|11018005#5#22#88#5|11018006#5#14#85#5|11018006#5#21#82#5|11018006#5#22#88#5</t>
+  </si>
+  <si>
+    <t>血色城堡19</t>
+  </si>
+  <si>
+    <t>11019001#8#14#21#3|11019002#8#14#24#3|11019003#8#14#27#3|11019004#8#14#31#3|11019001#8#14#34#3|11019002#8#14#37#3|11019003#8#14#41#3|11019004#8#14#44#3|11019001#8#14#47#3|11019002#8#14#51#3|11019003#8#14#54#3|11019004#8#14#57#3|11019001#8#14#59#3|11019002#8#14#61#3|11019003#8#14#64#3|11019005#5#14#85#5|11019005#5#21#82#5|11019005#5#22#88#5|11019006#5#14#85#5|11019006#5#21#82#5|11019006#5#22#88#5</t>
+  </si>
+  <si>
+    <t>血色城堡20</t>
+  </si>
+  <si>
+    <t>11020001#8#14#21#3|11020002#8#14#24#3|11020003#8#14#27#3|11020004#8#14#31#3|11020001#8#14#34#3|11020002#8#14#37#3|11020003#8#14#41#3|11020004#8#14#44#3|11020001#8#14#47#3|11020002#8#14#51#3|11020003#8#14#54#3|11020004#8#14#57#3|11020001#8#14#59#3|11020002#8#14#61#3|11020003#8#14#64#3|11020005#5#14#85#5|11020005#5#21#82#5|11020005#5#22#88#5|11020006#5#14#85#5|11020006#5#21#82#5|11020006#5#22#88#5</t>
+  </si>
+  <si>
+    <t>勇气试炼1</t>
+  </si>
+  <si>
+    <t>26001#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼2</t>
+  </si>
+  <si>
+    <t>26002#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼3</t>
+  </si>
+  <si>
+    <t>26003#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼4</t>
+  </si>
+  <si>
+    <t>26004#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼5</t>
+  </si>
+  <si>
+    <t>26005#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼6</t>
+  </si>
+  <si>
+    <t>26006#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼7</t>
+  </si>
+  <si>
+    <t>26007#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼8</t>
+  </si>
+  <si>
+    <t>26008#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼9</t>
+  </si>
+  <si>
+    <t>26009#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼10</t>
+  </si>
+  <si>
+    <t>26010#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼11</t>
+  </si>
+  <si>
+    <t>26011#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼12</t>
+  </si>
+  <si>
+    <t>26012#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼13</t>
+  </si>
+  <si>
+    <t>26013#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼14</t>
+  </si>
+  <si>
+    <t>26014#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼15</t>
+  </si>
+  <si>
+    <t>26015#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼16</t>
+  </si>
+  <si>
+    <t>26016#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼17</t>
+  </si>
+  <si>
+    <t>26017#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼18</t>
+  </si>
+  <si>
+    <t>26018#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼19</t>
+  </si>
+  <si>
+    <t>26019#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼20</t>
+  </si>
+  <si>
+    <t>26020#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼21</t>
+  </si>
+  <si>
+    <t>26021#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼22</t>
+  </si>
+  <si>
+    <t>26022#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼23</t>
+  </si>
+  <si>
+    <t>26023#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼24</t>
+  </si>
+  <si>
+    <t>26024#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼25</t>
+  </si>
+  <si>
+    <t>26025#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼26</t>
+  </si>
+  <si>
+    <t>26026#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼27</t>
+  </si>
+  <si>
+    <t>26027#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼28</t>
+  </si>
+  <si>
+    <t>26028#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼29</t>
+  </si>
+  <si>
+    <t>26029#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼30</t>
+  </si>
+  <si>
+    <t>26030#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼31</t>
+  </si>
+  <si>
+    <t>26031#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼32</t>
+  </si>
+  <si>
+    <t>26032#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼33</t>
+  </si>
+  <si>
+    <t>26033#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼34</t>
+  </si>
+  <si>
+    <t>26034#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼35</t>
+  </si>
+  <si>
+    <t>26035#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼36</t>
+  </si>
+  <si>
+    <t>26036#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼37</t>
+  </si>
+  <si>
+    <t>26037#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼38</t>
+  </si>
+  <si>
+    <t>26038#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼39</t>
+  </si>
+  <si>
+    <t>26039#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼40</t>
+  </si>
+  <si>
+    <t>26040#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼41</t>
+  </si>
+  <si>
+    <t>26041#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼42</t>
+  </si>
+  <si>
+    <t>26042#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼43</t>
+  </si>
+  <si>
+    <t>26043#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼44</t>
+  </si>
+  <si>
+    <t>26044#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼45</t>
+  </si>
+  <si>
+    <t>26045#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼46</t>
+  </si>
+  <si>
+    <t>26046#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼47</t>
+  </si>
+  <si>
+    <t>26047#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼48</t>
+  </si>
+  <si>
+    <t>26048#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼49</t>
+  </si>
+  <si>
+    <t>26049#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼50</t>
+  </si>
+  <si>
+    <t>26050#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼51</t>
+  </si>
+  <si>
+    <t>26051#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼52</t>
+  </si>
+  <si>
+    <t>26052#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼53</t>
+  </si>
+  <si>
+    <t>26053#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼54</t>
+  </si>
+  <si>
+    <t>26054#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼55</t>
+  </si>
+  <si>
+    <t>26055#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼56</t>
+  </si>
+  <si>
+    <t>26056#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼57</t>
+  </si>
+  <si>
+    <t>26057#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼58</t>
+  </si>
+  <si>
+    <t>26058#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼59</t>
+  </si>
+  <si>
+    <t>26059#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼60</t>
+  </si>
+  <si>
+    <t>26060#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼61</t>
+  </si>
+  <si>
+    <t>26061#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼62</t>
+  </si>
+  <si>
+    <t>26062#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼63</t>
+  </si>
+  <si>
+    <t>26063#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼64</t>
+  </si>
+  <si>
+    <t>26064#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼65</t>
+  </si>
+  <si>
+    <t>26065#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼66</t>
+  </si>
+  <si>
+    <t>26066#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼67</t>
+  </si>
+  <si>
+    <t>26067#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼68</t>
+  </si>
+  <si>
+    <t>26068#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼69</t>
+  </si>
+  <si>
+    <t>26069#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼70</t>
+  </si>
+  <si>
+    <t>26070#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼71</t>
+  </si>
+  <si>
+    <t>26071#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼72</t>
+  </si>
+  <si>
+    <t>26072#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼73</t>
+  </si>
+  <si>
+    <t>26073#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼74</t>
+  </si>
+  <si>
+    <t>26074#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼75</t>
+  </si>
+  <si>
+    <t>26075#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼76</t>
+  </si>
+  <si>
+    <t>26076#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼77</t>
+  </si>
+  <si>
+    <t>26077#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼78</t>
+  </si>
+  <si>
+    <t>26078#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼79</t>
+  </si>
+  <si>
+    <t>26079#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼80</t>
+  </si>
+  <si>
+    <t>26080#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼81</t>
+  </si>
+  <si>
+    <t>26081#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼82</t>
+  </si>
+  <si>
+    <t>26082#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼83</t>
+  </si>
+  <si>
+    <t>26083#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼84</t>
+  </si>
+  <si>
+    <t>26084#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼85</t>
+  </si>
+  <si>
+    <t>26085#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼86</t>
+  </si>
+  <si>
+    <t>26086#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼87</t>
+  </si>
+  <si>
+    <t>26087#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼88</t>
+  </si>
+  <si>
+    <t>26088#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼89</t>
+  </si>
+  <si>
+    <t>26089#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼90</t>
+  </si>
+  <si>
+    <t>26090#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼91</t>
+  </si>
+  <si>
+    <t>26091#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼92</t>
+  </si>
+  <si>
+    <t>26092#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼93</t>
+  </si>
+  <si>
+    <t>26093#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼94</t>
+  </si>
+  <si>
+    <t>26094#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼95</t>
+  </si>
+  <si>
+    <t>26095#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼96</t>
+  </si>
+  <si>
+    <t>26096#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼97</t>
+  </si>
+  <si>
+    <t>26097#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼98</t>
+  </si>
+  <si>
+    <t>26098#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼99</t>
+  </si>
+  <si>
+    <t>26099#1#31#212#1</t>
+  </si>
+  <si>
+    <t>勇气试炼100</t>
+  </si>
+  <si>
+    <t>26100#1#31#212#1</t>
+  </si>
+  <si>
+    <t>15001001#3#65#36#1|15001001#3#180#33#1|15001001#3#120#75#1|15001001#3#167#23#1|15001001#3#195#48#1|15001001#3#98#82#1|15001001#3#84#57#1|15001001#3#174#45#1|15001001#3#150#103#1|15001001#3#159#85#1|15001001#3#114#96#1|15001001#3#42#72#1|15001001#3#205#75#1|15001001#3#86#96#1|15001001#3#22#121#1|15001002#2#65#36#1|15001002#2#180#33#1|15001002#2#120#75#1|15001002#2#167#23#1|15001002#2#195#48#1|15001002#2#98#82#1|15001002#2#84#57#1|15001002#2#174#45#1|15001002#2#150#103#1|15001002#2#159#85#1|15001002#2#114#96#1|15001002#2#42#72#1|15001002#2#205#75#1|15001002#2#86#96#1|15001002#2#22#121#1|15001003#1#65#36#1|15001003#1#180#33#1|15001003#1#120#75#1|15001003#1#167#23#1|15001003#1#195#48#1|15001003#1#98#82#1|15001003#1#84#57#1|15001003#1#174#45#1|15001003#1#150#103#1|15001003#1#159#85#1|15001003#1#114#96#1|15001003#1#42#72#1|15001003#1#205#75#1|15001003#1#86#96#1|15001003#1#22#121#1</t>
+  </si>
+  <si>
     <t>10020001#1000|10090001#1500</t>
   </si>
   <si>
-    <t>狼魂要塞1副本-第2波</t>
-  </si>
-  <si>
-    <t>狼魂要塞1副本-第3波</t>
-  </si>
-  <si>
-    <t>15001004#3#83#33#1|15001004#3#120#69#1|15001004#3#158#31#1|15001004#3#80#30#1|15001004#3#118#72#1|15001004#3#161#35#1|15001004#3#81#35#1|15001004#3#124#72#1|15001004#3#162#29#1|15001004#3#75#29#1|15001004#3#117#75#1|15001004#3#164#36#1|15001004#3#76#35#1|15001004#3#122#75#1|15001005#2#83#33#1|15001005#2#120#69#1|15001005#2#158#31#1|15001005#2#80#30#1|15001005#2#118#72#1|15001005#2#161#35#1|15001005#2#81#35#1|15001005#2#124#72#1|15001005#2#162#29#1|15001005#2#75#29#1|15001005#2#117#75#1|15001005#2#164#36#1|15001005#2#76#35#1|15001005#2#122#75#1|15001006#1#83#33#1|15001006#1#120#69#1|15001006#1#158#31#1|15001006#1#80#30#1|15001006#1#118#72#1|15001006#1#161#35#1|15001006#1#81#35#1|15001006#1#124#72#1|15001006#1#162#29#1|15001006#1#75#29#1|15001006#1#117#75#1|15001006#1#164#36#1|15001006#1#76#35#1|15001006#1#122#75#1</t>
-  </si>
-  <si>
-    <t>狼魂要塞1副本-第4波</t>
-  </si>
-  <si>
-    <t>15001004#3#83#33#1|15001004#3#120#69#1|15001004#3#158#31#1|15001004#3#80#30#1|15001004#3#118#72#1|15001004#3#161#35#1|15001004#3#81#35#1|15001004#3#124#72#1|15001004#3#162#29#1|15001004#3#75#29#1|15001004#3#117#75#1|15001004#3#164#36#1|15001004#3#76#35#1|15001004#3#122#75#1|15001005#2#83#33#1|15001005#2#120#69#1|15001005#2#158#31#1|15001005#2#80#30#1|15001005#2#118#72#1|15001005#2#161#35#1|15001005#2#81#35#1|15001005#2#124#72#1|15001005#2#162#29#1|15001005#2#75#29#1|15001005#2#117#75#1|15001005#2#164#36#1|15001005#2#76#35#1|15001005#2#122#75#1|15001006#1#83#33#1|15001006#1#120#69#1|15001006#1#158#31#1|15001006#1#80#30#1|15001006#1#118#72#1|15001006#1#161#35#1|15001006#1#81#35#1|15001006#1#124#72#1|15001006#1#162#29#1|15001006#1#75#29#1|15001006#1#117#75#1|15001006#1#164#36#1|15001006#1#76#35#1|15001006#1#122#75#1|15001054#1#83#33#1|15001054#1#120#69#1|15001054#1#158#31#1</t>
-  </si>
-  <si>
-    <t>狼魂要塞1副本-第5波</t>
-  </si>
-  <si>
-    <t>15001007#3#83#33#1|15001007#3#120#69#1|15001007#3#158#31#1|15001007#3#80#30#1|15001007#3#118#72#1|15001007#3#161#35#1|15001007#3#81#35#1|15001007#3#124#72#1|15001007#3#162#29#1|15001007#3#75#29#1|15001007#3#117#75#1|15001007#3#164#36#1|15001007#3#76#35#1|15001008#2#83#33#1|15001008#2#120#69#1|15001008#2#158#31#1|15001008#2#80#30#1|15001008#2#118#72#1|15001008#2#161#35#1|15001008#2#81#35#1|15001008#2#124#72#1|15001008#2#162#29#1|15001008#2#75#29#1|15001008#2#117#75#1|15001008#2#164#36#1|15001008#2#76#35#1|15001009#1#83#33#1|15001009#1#120#69#1|15001009#1#158#31#1|15001009#1#80#30#1|15001009#1#118#72#1|15001009#1#161#35#1|15001009#1#81#35#1|15001009#1#124#72#1|15001009#1#162#29#1|15001009#1#75#29#1|15001009#1#117#75#1|15001009#1#164#36#1|15001009#1#76#35#1</t>
+    <t>15001004#3#65#36#1|15001004#3#180#33#1|15001004#3#120#75#1|15001004#3#167#23#1|15001004#3#195#48#1|15001004#3#98#82#1|15001004#3#84#57#1|15001004#3#174#45#1|15001004#3#150#103#1|15001004#3#159#85#1|15001004#3#114#96#1|15001004#3#42#72#1|15001004#3#205#75#1|15001004#3#86#96#1|15001005#2#65#36#1|15001005#2#180#33#1|15001005#2#120#75#1|15001005#2#167#23#1|15001005#2#195#48#1|15001005#2#98#82#1|15001005#2#84#57#1|15001005#2#174#45#1|15001005#2#150#103#1|15001005#2#159#85#1|15001005#2#114#96#1|15001005#2#42#72#1|15001005#2#205#75#1|15001005#2#86#96#1|15001006#1#65#36#1|15001006#1#180#33#1|15001006#1#120#75#1|15001006#1#167#23#1|15001006#1#195#48#1|15001006#1#98#82#1|15001006#1#84#57#1|15001006#1#174#45#1|15001006#1#150#103#1|15001006#1#159#85#1|15001006#1#114#96#1|15001006#1#42#72#1|15001006#1#205#75#1|15001006#1#86#96#1</t>
+  </si>
+  <si>
+    <t>15001007#3#65#36#1|15001007#3#180#33#1|15001007#3#120#75#1|15001007#3#167#23#1|15001007#3#195#48#1|15001007#3#98#82#1|15001007#3#84#57#1|15001007#3#174#45#1|15001007#3#150#103#1|15001007#3#159#85#1|15001007#3#114#96#1|15001007#3#42#72#1|15001007#3#205#75#1|15001008#2#65#36#1|15001008#2#180#33#1|15001008#2#120#75#1|15001008#2#167#23#1|15001008#2#195#48#1|15001008#2#98#82#1|15001008#2#84#57#1|15001008#2#174#45#1|15001008#2#150#103#1|15001008#2#159#85#1|15001008#2#114#96#1|15001008#2#42#72#1|15001008#2#205#75#1|15001009#1#65#36#1|15001009#1#180#33#1|15001009#1#120#75#1|15001009#1#167#23#1|15001009#1#195#48#1|15001009#1#98#82#1|15001009#1#84#57#1|15001009#1#174#45#1|15001009#1#150#103#1|15001009#1#159#85#1|15001009#1#114#96#1|15001009#1#42#72#1|15001009#1#205#75#1</t>
   </si>
   <si>
     <t>10020001#2000|10090001#2000</t>
   </si>
   <si>
-    <t>狼魂要塞1副本-第6波</t>
-  </si>
-  <si>
-    <t>狼魂要塞1副本-第7波</t>
-  </si>
-  <si>
-    <t>15001010#3#83#33#1|15001010#3#120#69#1|15001010#3#158#31#1|15001010#3#80#30#1|15001010#3#118#72#1|15001010#3#161#35#1|15001010#3#81#35#1|15001010#3#124#72#1|15001010#3#162#29#1|15001010#3#75#29#1|15001010#3#117#75#1|15001010#3#164#36#1|15001011#2#83#33#1|15001011#2#120#69#1|15001011#2#158#31#1|15001011#2#80#30#1|15001011#2#118#72#1|15001011#2#161#35#1|15001011#2#81#35#1|15001011#2#124#72#1|15001011#2#162#29#1|15001011#2#75#29#1|15001011#2#117#75#1|15001011#2#164#36#1|15001012#1#83#33#1|15001012#1#120#69#1|15001012#1#158#31#1|15001012#1#80#30#1|15001012#1#118#72#1|15001012#1#161#35#1|15001012#1#81#35#1|15001012#1#124#72#1|15001012#1#162#29#1|15001012#1#75#29#1|15001012#1#117#75#1|15001012#1#164#36#1</t>
-  </si>
-  <si>
-    <t>狼魂要塞1副本-第8波</t>
-  </si>
-  <si>
-    <t>15001010#3#83#33#1|15001010#3#120#69#1|15001010#3#158#31#1|15001010#3#80#30#1|15001010#3#118#72#1|15001010#3#161#35#1|15001010#3#81#35#1|15001010#3#124#72#1|15001010#3#162#29#1|15001010#3#75#29#1|15001010#3#117#75#1|15001010#3#164#36#1|15001011#2#83#33#1|15001011#2#120#69#1|15001011#2#158#31#1|15001011#2#80#30#1|15001011#2#118#72#1|15001011#2#161#35#1|15001011#2#81#35#1|15001011#2#124#72#1|15001011#2#162#29#1|15001011#2#75#29#1|15001011#2#117#75#1|15001011#2#164#36#1|15001012#1#83#33#1|15001012#1#120#69#1|15001012#1#158#31#1|15001012#1#80#30#1|15001012#1#118#72#1|15001012#1#161#35#1|15001012#1#81#35#1|15001012#1#124#72#1|15001012#1#162#29#1|15001012#1#75#29#1|15001012#1#117#75#1|15001012#1#164#36#1|15001054#1#83#33#1|15001054#1#120#69#1|15001054#1#158#31#1</t>
-  </si>
-  <si>
-    <t>狼魂要塞1副本-第9波</t>
-  </si>
-  <si>
-    <t>15001013#3#83#33#1|15001013#3#120#69#1|15001013#3#158#31#1|15001013#3#80#30#1|15001013#3#118#72#1|15001013#3#161#35#1|15001013#3#81#35#1|15001013#3#124#72#1|15001013#3#162#29#1|15001013#3#75#29#1|15001013#3#117#75#1|15001014#2#83#33#1|15001014#2#120#69#1|15001014#2#158#31#1|15001014#2#80#30#1|15001014#2#118#72#1|15001014#2#161#35#1|15001014#2#81#35#1|15001014#2#124#72#1|15001014#2#162#29#1|15001014#2#75#29#1|15001014#2#117#75#1|15001015#1#83#33#1|15001015#1#120#69#1|15001015#1#158#31#1|15001015#1#80#30#1|15001015#1#118#72#1|15001015#1#161#35#1|15001015#1#81#35#1|15001015#1#124#72#1|15001015#1#162#29#1|15001015#1#75#29#1|15001015#1#117#75#1</t>
-  </si>
-  <si>
-    <t>狼魂要塞1副本-第10波</t>
+    <t>15001010#3#65#36#1|15001010#3#180#33#1|15001010#3#120#75#1|15001010#3#167#23#1|15001010#3#195#48#1|15001010#3#98#82#1|15001010#3#84#57#1|15001010#3#174#45#1|15001010#3#150#103#1|15001010#3#159#85#1|15001010#3#114#96#1|15001010#3#42#72#1|15001011#2#65#36#1|15001011#2#180#33#1|15001011#2#120#75#1|15001011#2#167#23#1|15001011#2#195#48#1|15001011#2#98#82#1|15001011#2#84#57#1|15001011#2#174#45#1|15001011#2#150#103#1|15001011#2#159#85#1|15001011#2#114#96#1|15001011#2#42#72#1|15001012#1#65#36#1|15001012#1#180#33#1|15001012#1#120#75#1|15001012#1#167#23#1|15001012#1#195#48#1|15001012#1#98#82#1|15001012#1#84#57#1|15001012#1#174#45#1|15001012#1#150#103#1|15001012#1#159#85#1|15001012#1#114#96#1|15001012#1#42#72#1</t>
+  </si>
+  <si>
+    <t>15001013#3#65#36#1|15001013#3#180#33#1|15001013#3#120#75#1|15001013#3#167#23#1|15001013#3#195#48#1|15001013#3#98#82#1|15001013#3#84#57#1|15001013#3#174#45#1|15001013#3#150#103#1|15001013#3#159#85#1|15001013#3#114#96#1|15001014#2#65#36#1|15001014#2#180#33#1|15001014#2#120#75#1|15001014#2#167#23#1|15001014#2#195#48#1|15001014#2#98#82#1|15001014#2#84#57#1|15001014#2#174#45#1|15001014#2#150#103#1|15001014#2#159#85#1|15001014#2#114#96#1|15001015#1#65#36#1|15001015#1#180#33#1|15001015#1#120#75#1|15001015#1#167#23#1|15001015#1#195#48#1|15001015#1#98#82#1|15001015#1#84#57#1|15001015#1#174#45#1|15001015#1#150#103#1|15001015#1#159#85#1|15001015#1#114#96#1</t>
   </si>
   <si>
     <t>10020001#3000|10090001#2500</t>
   </si>
   <si>
-    <t>狼魂要塞1副本-第11波</t>
-  </si>
-  <si>
-    <t>15001016#3#83#33#1|15001016#3#120#69#1|15001016#3#158#31#1|15001016#3#80#30#1|15001016#3#118#72#1|15001016#3#161#35#1|15001016#3#81#35#1|15001016#3#124#72#1|15001016#3#162#29#1|15001016#3#75#29#1|15001017#2#83#33#1|15001017#2#120#69#1|15001017#2#158#31#1|15001017#2#80#30#1|15001017#2#118#72#1|15001017#2#161#35#1|15001017#2#81#35#1|15001017#2#124#72#1|15001017#2#162#29#1|15001017#2#75#29#1|15001018#1#83#33#1|15001018#1#120#69#1|15001018#1#158#31#1|15001018#1#80#30#1|15001018#1#118#72#1|15001018#1#161#35#1|15001018#1#81#35#1|15001018#1#124#72#1|15001018#1#162#29#1|15001018#1#75#29#1</t>
-  </si>
-  <si>
-    <t>狼魂要塞1副本-第12波</t>
-  </si>
-  <si>
-    <t>15001016#3#83#33#1|15001016#3#120#69#1|15001016#3#158#31#1|15001016#3#80#30#1|15001016#3#118#72#1|15001016#3#161#35#1|15001016#3#81#35#1|15001016#3#124#72#1|15001016#3#162#29#1|15001016#3#75#29#1|15001017#2#83#33#1|15001017#2#120#69#1|15001017#2#158#31#1|15001017#2#80#30#1|15001017#2#118#72#1|15001017#2#161#35#1|15001017#2#81#35#1|15001017#2#124#72#1|15001017#2#162#29#1|15001017#2#75#29#1|15001018#1#83#33#1|15001018#1#120#69#1|15001018#1#158#31#1|15001018#1#80#30#1|15001018#1#118#72#1|15001018#1#161#35#1|15001018#1#81#35#1|15001018#1#124#72#1|15001018#1#162#29#1|15001018#1#75#29#1|15001054#1#83#33#1|15001054#1#120#69#1|15001054#1#158#31#1</t>
-  </si>
-  <si>
-    <t>狼魂要塞1副本-第13波</t>
-  </si>
-  <si>
-    <t>15001019#3#83#33#1|15001019#3#120#69#1|15001019#3#158#31#1|15001019#3#80#30#1|15001019#3#118#72#1|15001019#3#161#35#1|15001019#3#81#35#1|15001019#3#124#72#1|15001019#3#162#29#1|15001020#2#83#33#1|15001020#2#120#69#1|15001020#2#158#31#1|15001020#2#80#30#1|15001020#2#118#72#1|15001020#2#161#35#1|15001020#2#81#35#1|15001020#2#124#72#1|15001020#2#162#29#1|15001021#1#83#33#1|15001021#1#120#69#1|15001021#1#158#31#1|15001021#1#80#30#1|15001021#1#118#72#1|15001021#1#161#35#1|15001021#1#81#35#1|15001021#1#124#72#1|15001021#1#162#29#1</t>
-  </si>
-  <si>
-    <t>狼魂要塞1副本-第14波</t>
-  </si>
-  <si>
-    <t>狼魂要塞1副本-第15波</t>
-  </si>
-  <si>
-    <t>15001022#3#83#33#1|15001022#3#120#69#1|15001022#3#158#31#1|15001022#3#80#30#1|15001022#3#118#72#1|15001022#3#161#35#1|15001022#3#81#35#1|15001022#3#124#72#1|15001022#3#162#29#1|15001023#2#83#33#1|15001023#2#120#69#1|15001023#2#158#31#1|15001023#2#80#30#1|15001023#2#118#72#1|15001023#2#161#35#1|15001023#2#81#35#1|15001023#2#124#72#1|15001023#2#162#29#1|15001024#1#83#33#1|15001024#1#120#69#1|15001024#1#158#31#1|15001024#1#80#30#1|15001024#1#118#72#1|15001024#1#161#35#1|15001024#1#81#35#1|15001024#1#124#72#1|15001024#1#162#29#1</t>
-  </si>
-  <si>
-    <t>狼魂要塞1副本-第16波</t>
-  </si>
-  <si>
-    <t>15001022#3#83#33#1|15001022#3#120#69#1|15001022#3#158#31#1|15001022#3#80#30#1|15001022#3#118#72#1|15001022#3#161#35#1|15001022#3#81#35#1|15001022#3#124#72#1|15001022#3#162#29#1|15001023#2#83#33#1|15001023#2#120#69#1|15001023#2#158#31#1|15001023#2#80#30#1|15001023#2#118#72#1|15001023#2#161#35#1|15001023#2#81#35#1|15001023#2#124#72#1|15001023#2#162#29#1|15001024#1#83#33#1|15001024#1#120#69#1|15001024#1#158#31#1|15001024#1#80#30#1|15001024#1#118#72#1|15001024#1#161#35#1|15001024#1#81#35#1|15001024#1#124#72#1|15001024#1#162#29#1|15001054#1#83#33#1|15001054#1#120#69#1|15001054#1#158#31#1</t>
+    <t>15001016#3#65#36#1|15001016#3#180#33#1|15001016#3#120#75#1|15001016#3#167#23#1|15001016#3#195#48#1|15001016#3#98#82#1|15001016#3#84#57#1|15001016#3#174#45#1|15001016#3#150#103#1|15001016#3#159#85#1|15001017#2#65#36#1|15001017#2#180#33#1|15001017#2#120#75#1|15001017#2#167#23#1|15001017#2#195#48#1|15001017#2#98#82#1|15001017#2#84#57#1|15001017#2#174#45#1|15001017#2#150#103#1|15001017#2#159#85#1|15001018#1#65#36#1|15001018#1#180#33#1|15001018#1#120#75#1|15001018#1#167#23#1|15001018#1#195#48#1|15001018#1#98#82#1|15001018#1#84#57#1|15001018#1#174#45#1|15001018#1#150#103#1|15001018#1#159#85#1</t>
+  </si>
+  <si>
+    <t>15001019#3#65#36#1|15001019#3#180#33#1|15001019#3#120#75#1|15001019#3#167#23#1|15001019#3#195#48#1|15001019#3#98#82#1|15001019#3#84#57#1|15001019#3#174#45#1|15001019#3#150#103#1|15001020#2#65#36#1|15001020#2#180#33#1|15001020#2#120#75#1|15001020#2#167#23#1|15001020#2#195#48#1|15001020#2#98#82#1|15001020#2#84#57#1|15001020#2#174#45#1|15001020#2#150#103#1|15001021#1#65#36#1|15001021#1#180#33#1|15001021#1#120#75#1|15001021#1#167#23#1|15001021#1#195#48#1|15001021#1#98#82#1|15001021#1#84#57#1|15001021#1#174#45#1|15001021#1#150#103#1</t>
+  </si>
+  <si>
+    <t>15001022#3#65#36#1|15001022#3#180#33#1|15001022#3#120#75#1|15001022#3#167#23#1|15001022#3#195#48#1|15001022#3#98#82#1|15001022#3#84#57#1|15001022#3#174#45#1|15001022#3#150#103#1|15001023#2#65#36#1|15001023#2#180#33#1|15001023#2#120#75#1|15001023#2#167#23#1|15001023#2#195#48#1|15001023#2#98#82#1|15001023#2#84#57#1|15001023#2#174#45#1|15001023#2#150#103#1|15001024#1#65#36#1|15001024#1#180#33#1|15001024#1#120#75#1|15001024#1#167#23#1|15001024#1#195#48#1|15001024#1#98#82#1|15001024#1#84#57#1|15001024#1#174#45#1|15001024#1#150#103#1</t>
   </si>
   <si>
     <t>10020001#4000|10090001#3000</t>
   </si>
   <si>
-    <t>狼魂要塞1副本-第17波</t>
-  </si>
-  <si>
-    <t>15001025#3#83#33#1|15001025#3#120#69#1|15001025#3#158#31#1|15001025#3#80#30#1|15001025#3#118#72#1|15001025#3#161#35#1|15001025#3#81#35#1|15001025#3#124#72#1|15001025#3#162#29#1|15001026#2#83#33#1|15001026#2#120#69#1|15001026#2#158#31#1|15001026#2#80#30#1|15001026#2#118#72#1|15001026#2#161#35#1|15001026#2#81#35#1|15001026#2#124#72#1|15001026#2#162#29#1|15001027#1#83#33#1|15001027#1#120#69#1|15001027#1#158#31#1|15001027#1#80#30#1|15001027#1#118#72#1|15001027#1#161#35#1|15001027#1#81#35#1|15001027#1#124#72#1|15001027#1#162#29#1</t>
-  </si>
-  <si>
-    <t>狼魂要塞1副本-第18波</t>
-  </si>
-  <si>
-    <t>狼魂要塞1副本-第19波</t>
-  </si>
-  <si>
-    <t>15001028#3#83#33#1|15001028#3#120#69#1|15001028#3#158#31#1|15001028#3#80#30#1|15001028#3#118#72#1|15001028#3#161#35#1|15001028#3#81#35#1|15001028#3#124#72#1|15001028#3#162#29#1|15001029#2#83#33#1|15001029#2#120#69#1|15001029#2#158#31#1|15001029#2#80#30#1|15001029#2#118#72#1|15001029#2#161#35#1|15001029#2#81#35#1|15001029#2#124#72#1|15001029#2#162#29#1|15001030#1#83#33#1|15001030#1#120#69#1|15001030#1#158#31#1|15001030#1#80#30#1|15001030#1#118#72#1|15001030#1#161#35#1|15001030#1#81#35#1|15001030#1#124#72#1|15001030#1#162#29#1</t>
-  </si>
-  <si>
-    <t>狼魂要塞1副本-第20波</t>
-  </si>
-  <si>
-    <t>15001028#3#83#33#1|15001028#3#120#69#1|15001028#3#158#31#1|15001028#3#80#30#1|15001028#3#118#72#1|15001028#3#161#35#1|15001028#3#81#35#1|15001028#3#124#72#1|15001028#3#162#29#1|15001029#2#83#33#1|15001029#2#120#69#1|15001029#2#158#31#1|15001029#2#80#30#1|15001029#2#118#72#1|15001029#2#161#35#1|15001029#2#81#35#1|15001029#2#124#72#1|15001029#2#162#29#1|15001030#1#83#33#1|15001030#1#120#69#1|15001030#1#158#31#1|15001030#1#80#30#1|15001030#1#118#72#1|15001030#1#161#35#1|15001030#1#81#35#1|15001030#1#124#72#1|15001030#1#162#29#1|15001055#1#83#33#1|15001055#1#120#69#1</t>
+    <t>15001025#3#65#36#1|15001025#3#180#33#1|15001025#3#120#75#1|15001025#3#167#23#1|15001025#3#195#48#1|15001025#3#98#82#1|15001025#3#84#57#1|15001025#3#174#45#1|15001025#3#150#103#1|15001026#2#65#36#1|15001026#2#180#33#1|15001026#2#120#75#1|15001026#2#167#23#1|15001026#2#195#48#1|15001026#2#98#82#1|15001026#2#84#57#1|15001026#2#174#45#1|15001026#2#150#103#1|15001027#1#65#36#1|15001027#1#180#33#1|15001027#1#120#75#1|15001027#1#167#23#1|15001027#1#195#48#1|15001027#1#98#82#1|15001027#1#84#57#1|15001027#1#174#45#1|15001027#1#150#103#1</t>
+  </si>
+  <si>
+    <t>15001028#3#65#36#1|15001028#3#180#33#1|15001028#3#120#75#1|15001028#3#167#23#1|15001028#3#195#48#1|15001028#3#98#82#1|15001028#3#84#57#1|15001028#3#174#45#1|15001028#3#150#103#1|15001029#2#65#36#1|15001029#2#180#33#1|15001029#2#120#75#1|15001029#2#167#23#1|15001029#2#195#48#1|15001029#2#98#82#1|15001029#2#84#57#1|15001029#2#174#45#1|15001029#2#150#103#1|15001030#1#65#36#1|15001030#1#180#33#1|15001030#1#120#75#1|15001030#1#167#23#1|15001030#1#195#48#1|15001030#1#98#82#1|15001030#1#84#57#1|15001030#1#174#45#1|15001030#1#150#103#1</t>
   </si>
   <si>
     <t>10020001#14000|10090001#7000</t>
-  </si>
-  <si>
-    <t>卡利玛神庙第1关</t>
-  </si>
-  <si>
-    <t>102500009#1#40#97#2|102500001#10#57#24#5|102500001#10#81#21#5|102500002#10#100#18#5|102500002#10#110#38#5|102500003#10#115#58#5|102500003#10#113#77#5|102500004#10#102#99#5|102500006#10#35#58#5|102500007#10#36#79#5</t>
-  </si>
-  <si>
-    <t>卡利玛神庙第2关</t>
-  </si>
-  <si>
-    <t>102500019#1#40#97#2|102500011#10#57#24#5|102500011#10#81#21#5|102500012#10#100#18#5|102500012#10#110#38#5|102500013#10#115#58#5|102500013#10#113#77#5|102500014#10#102#99#5|102500016#10#35#58#5|102500017#10#36#79#5</t>
-  </si>
-  <si>
-    <t>卡利玛神庙第3关</t>
-  </si>
-  <si>
-    <t>102500029#1#40#97#2|102500021#10#57#24#5|102500021#10#81#21#5|102500022#10#100#18#5|102500022#10#110#38#5|102500023#10#115#58#5|102500023#10#113#77#5|102500024#10#102#99#5|102500026#10#35#58#5|102500027#10#36#79#5</t>
-  </si>
-  <si>
-    <t>卡利玛神庙第4关</t>
-  </si>
-  <si>
-    <t>102500039#1#40#97#2|102500031#10#57#24#5|102500031#10#81#21#5|102500032#10#100#18#5|102500032#10#110#38#5|102500033#10#115#58#5|102500033#10#113#77#5|102500034#10#102#99#5|102500036#10#35#58#5|102500037#10#36#79#5</t>
-  </si>
-  <si>
-    <t>卡利玛神庙第5关</t>
-  </si>
-  <si>
-    <t>102500049#1#40#97#2|102500041#10#57#24#5|102500041#10#81#21#5|102500042#10#100#18#5|102500042#10#110#38#5|102500043#10#115#58#5|102500043#10#113#77#5|102500044#10#102#99#5|102500046#10#35#58#5|102500047#10#36#79#5</t>
-  </si>
-  <si>
-    <t>卡利玛神庙第6关</t>
-  </si>
-  <si>
-    <t>102500059#1#40#97#2|102500051#10#57#24#5|102500051#10#81#21#5|102500052#10#100#18#5|102500052#10#110#38#5|102500053#10#115#58#5|102500053#10#113#77#5|102500054#10#102#99#5|102500056#10#35#58#5|102500057#10#36#79#5</t>
-  </si>
-  <si>
-    <t>卡利玛神庙第7关</t>
-  </si>
-  <si>
-    <t>102500069#1#40#97#2|102500061#10#57#24#5|102500061#10#81#21#5|102500062#10#100#18#5|102500062#10#110#38#5|102500063#10#115#58#5|102500063#10#113#77#5|102500064#10#102#99#5|102500066#10#35#58#5|102500067#10#36#79#5</t>
-  </si>
-  <si>
-    <t>50005#20#127#104#10|50003#20#127#88#10|50005#20#142#88#10|50003#20#142#104#10|50006#20#137#92#10</t>
-  </si>
-  <si>
-    <t>50003#20#127#104#10|50006#20#127#88#10|50010#20#142#88#10|50003#20#142#104#10|50006#20#137#92#10</t>
-  </si>
-  <si>
-    <t>50003#20#127#104#10|50003#20#127#88#10|50005#20#142#88#10|50003#20#142#104#10|50006#20#137#92#10</t>
-  </si>
-  <si>
-    <t>50008#20#127#104#10|50009#20#127#88#10|50009#20#142#88#10|50008#20#142#104#10|50009#20#137#92#10</t>
-  </si>
-  <si>
-    <t>60001#20#127#104#10|60002#20#127#88#10|60003#20#142#88#10|60001#20#142#104#10|60002#20#137#92#10</t>
-  </si>
-  <si>
-    <t>60002#20#127#104#10|60003#20#127#88#10|60004#20#142#88#10|60002#20#142#104#10|60003#20#137#92#10</t>
-  </si>
-  <si>
-    <t>60004#20#127#104#10|60005#20#127#88#10|60006#20#142#88#10|60004#20#142#104#10|60005#20#137#92#10</t>
-  </si>
-  <si>
-    <t>60006#20#127#104#10|60007#20#127#88#10|60007#20#142#88#10|60005#20#142#104#10|60006#20#137#92#10</t>
-  </si>
-  <si>
-    <t>70001#20#127#104#10|70002#20#127#88#10|70003#20#142#88#10|70001#20#142#104#10|70002#20#137#92#10</t>
-  </si>
-  <si>
-    <t>70002#20#127#104#10|70003#20#127#88#10|70004#20#142#88#10|70002#20#142#104#10|70003#20#137#92#10</t>
-  </si>
-  <si>
-    <t>70003#20#127#104#10|70004#20#127#88#10|70005#20#142#88#10|70003#20#142#104#10|70004#20#137#92#10</t>
-  </si>
-  <si>
-    <t>70004#20#127#104#10|70005#20#127#88#10|70006#20#142#88#10|70004#20#142#104#10|70005#20#137#92#10</t>
-  </si>
-  <si>
-    <t>22001#20#127#104#10|22002#20#127#88#10|24004#20#142#88#10|22001#20#142#104#10|22002#20#137#92#10</t>
-  </si>
-  <si>
-    <t>22002#20#127#104#10|24004#20#127#88#10|24003#20#142#88#10|22002#20#142#104#10|24004#20#137#92#10</t>
-  </si>
-  <si>
-    <t>24003#20#127#104#10|80005#20#127#88#10|90003#20#142#88#10|24003#20#142#104#10|80005#20#137#92#10</t>
-  </si>
-  <si>
-    <t>80001#20#127#104#10|80002#20#127#88#10|80003#20#142#88#10|80001#20#142#104#10|80002#20#137#92#10</t>
-  </si>
-  <si>
-    <t>80002#20#127#104#10|80003#20#127#88#10|80004#20#142#88#10|80002#20#142#104#10|80003#20#137#92#10</t>
-  </si>
-  <si>
-    <t>80003#20#127#104#10|80004#20#127#88#10|80005#20#142#88#10|80003#20#142#104#10|80004#20#137#92#10</t>
-  </si>
-  <si>
-    <t>24005#20#127#104#10|24006#20#127#88#10|24007#20#142#88#10|24005#20#142#104#10|24006#20#137#92#10</t>
-  </si>
-  <si>
-    <t>90002#20#127#104#10|90001#20#127#88#10|90004#20#142#88#10|90002#20#142#104#10|90001#20#137#92#10</t>
-  </si>
-  <si>
-    <t>90001#20#127#104#10|90004#20#127#88#10|90005#20#142#88#10|90001#20#142#104#10|90005#20#137#92#10</t>
-  </si>
-  <si>
-    <t>90004#20#127#104#10|90005#20#127#88#10|90006#20#142#88#10|90004#20#142#104#10|90005#20#137#92#10</t>
-  </si>
-  <si>
-    <t>12006#20#127#104#10|12007#20#127#88#10|90006#20#142#88#10|90004#20#142#104#10|90005#20#137#92#10</t>
-  </si>
-  <si>
-    <t>12007#20#127#104#10|13001#20#127#88#10|13002#20#142#88#10|13001#20#142#104#10|13002#20#137#92#10</t>
-  </si>
-  <si>
-    <t>13001#20#127#104#10|13002#20#127#88#10|13003#20#142#88#10|13001#20#142#104#10|13002#20#137#92#10</t>
-  </si>
-  <si>
-    <t>恶魔广场8层1波</t>
-  </si>
-  <si>
-    <t>10008001#11#144#107#10|10008001#11#144#89#10|10008001#11#135#98#10|10008001#11#126#107#10|10008001#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场8层2波</t>
-  </si>
-  <si>
-    <t>10008002#11#144#107#10|10008002#11#144#89#10|10008002#11#135#98#10|10008002#11#126#107#10|10008002#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场8层3波</t>
-  </si>
-  <si>
-    <t>10008003#11#144#107#10|10008003#11#144#89#10|10008003#11#135#98#10|10008003#11#126#107#10|10008003#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场8层4波</t>
-  </si>
-  <si>
-    <t>10008004#11#144#107#10|10008004#11#144#89#10|10008004#11#135#98#10|10008004#11#126#107#10|10008004#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场9层1波</t>
-  </si>
-  <si>
-    <t>10009001#11#144#107#10|10009001#11#144#89#10|10009001#11#135#98#10|10009001#11#126#107#10|10009001#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场9层2波</t>
-  </si>
-  <si>
-    <t>10009002#11#144#107#10|10009002#11#144#89#10|10009002#11#135#98#10|10009002#11#126#107#10|10009002#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场9层3波</t>
-  </si>
-  <si>
-    <t>10009003#11#144#107#10|10009003#11#144#89#10|10009003#11#135#98#10|10009003#11#126#107#10|10009003#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场9层4波</t>
-  </si>
-  <si>
-    <t>10009004#11#144#107#10|10009004#11#144#89#10|10009004#11#135#98#10|10009004#11#126#107#10|10009004#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场10层1波</t>
-  </si>
-  <si>
-    <t>10010001#11#144#107#10|10010001#11#144#89#10|10010001#11#135#98#10|10010001#11#126#107#10|10010001#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场10层2波</t>
-  </si>
-  <si>
-    <t>10010002#11#144#107#10|10010002#11#144#89#10|10010002#11#135#98#10|10010002#11#126#107#10|10010002#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场10层3波</t>
-  </si>
-  <si>
-    <t>10010003#11#144#107#10|10010003#11#144#89#10|10010003#11#135#98#10|10010003#11#126#107#10|10010003#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场10层4波</t>
-  </si>
-  <si>
-    <t>10010004#11#144#107#10|10010004#11#144#89#10|10010004#11#135#98#10|10010004#11#126#107#10|10010004#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场11层1波</t>
-  </si>
-  <si>
-    <t>10011001#11#144#107#10|10011001#11#144#89#10|10011001#11#135#98#10|10011001#11#126#107#10|10011001#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场11层2波</t>
-  </si>
-  <si>
-    <t>10011002#11#144#107#10|10011002#11#144#89#10|10011002#11#135#98#10|10011002#11#126#107#10|10011002#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场11层3波</t>
-  </si>
-  <si>
-    <t>10011003#11#144#107#10|10011003#11#144#89#10|10011003#11#135#98#10|10011003#11#126#107#10|10011003#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场11层4波</t>
-  </si>
-  <si>
-    <t>10011004#11#144#107#10|10011004#11#144#89#10|10011004#11#135#98#10|10011004#11#126#107#10|10011004#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场12层1波</t>
-  </si>
-  <si>
-    <t>10012001#11#144#107#10|10012001#11#144#89#10|10012001#11#135#98#10|10012001#11#126#107#10|10012001#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场12层2波</t>
-  </si>
-  <si>
-    <t>10012002#11#144#107#10|10012002#11#144#89#10|10012002#11#135#98#10|10012002#11#126#107#10|10012002#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场12层3波</t>
-  </si>
-  <si>
-    <t>10012003#11#144#107#10|10012003#11#144#89#10|10012003#11#135#98#10|10012003#11#126#107#10|10012003#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场12层4波</t>
-  </si>
-  <si>
-    <t>10012004#11#144#107#10|10012004#11#144#89#10|10012004#11#135#98#10|10012004#11#126#107#10|10012004#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场13层1波</t>
-  </si>
-  <si>
-    <t>10013001#11#144#107#10|10013001#11#144#89#10|10013001#11#135#98#10|10013001#11#126#107#10|10013001#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场13层2波</t>
-  </si>
-  <si>
-    <t>10013002#11#144#107#10|10013002#11#144#89#10|10013002#11#135#98#10|10013002#11#126#107#10|10013002#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场13层3波</t>
-  </si>
-  <si>
-    <t>10013003#11#144#107#10|10013003#11#144#89#10|10013003#11#135#98#10|10013003#11#126#107#10|10013003#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场13层4波</t>
-  </si>
-  <si>
-    <t>10013004#11#144#107#10|10013004#11#144#89#10|10013004#11#135#98#10|10013004#11#126#107#10|10013004#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场14层1波</t>
-  </si>
-  <si>
-    <t>10014001#11#144#107#10|10014001#11#144#89#10|10014001#11#135#98#10|10014001#11#126#107#10|10014001#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场14层2波</t>
-  </si>
-  <si>
-    <t>10014002#11#144#107#10|10014002#11#144#89#10|10014002#11#135#98#10|10014002#11#126#107#10|10014002#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场14层3波</t>
-  </si>
-  <si>
-    <t>10014003#11#144#107#10|10014003#11#144#89#10|10014003#11#135#98#10|10014003#11#126#107#10|10014003#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场14层4波</t>
-  </si>
-  <si>
-    <t>10014004#11#144#107#10|10014004#11#144#89#10|10014004#11#135#98#10|10014004#11#126#107#10|10014004#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场15层1波</t>
-  </si>
-  <si>
-    <t>10015001#11#144#107#10|10015001#11#144#89#10|10015001#11#135#98#10|10015001#11#126#107#10|10015001#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场15层2波</t>
-  </si>
-  <si>
-    <t>10015002#11#144#107#10|10015002#11#144#89#10|10015002#11#135#98#10|10015002#11#126#107#10|10015002#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场15层3波</t>
-  </si>
-  <si>
-    <t>10015003#11#144#107#10|10015003#11#144#89#10|10015003#11#135#98#10|10015003#11#126#107#10|10015003#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场15层4波</t>
-  </si>
-  <si>
-    <t>10015004#11#144#107#10|10015004#11#144#89#10|10015004#11#135#98#10|10015004#11#126#107#10|10015004#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场16层1波</t>
-  </si>
-  <si>
-    <t>10016001#11#144#107#10|10016001#11#144#89#10|10016001#11#135#98#10|10016001#11#126#107#10|10016001#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场16层2波</t>
-  </si>
-  <si>
-    <t>10016002#11#144#107#10|10016002#11#144#89#10|10016002#11#135#98#10|10016002#11#126#107#10|10016002#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场16层3波</t>
-  </si>
-  <si>
-    <t>10016003#11#144#107#10|10016003#11#144#89#10|10016003#11#135#98#10|10016003#11#126#107#10|10016003#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场16层4波</t>
-  </si>
-  <si>
-    <t>10016004#11#144#107#10|10016004#11#144#89#10|10016004#11#135#98#10|10016004#11#126#107#10|10016004#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场17层1波</t>
-  </si>
-  <si>
-    <t>10017001#11#144#107#10|10017001#11#144#89#10|10017001#11#135#98#10|10017001#11#126#107#10|10017001#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场17层2波</t>
-  </si>
-  <si>
-    <t>10017002#11#144#107#10|10017002#11#144#89#10|10017002#11#135#98#10|10017002#11#126#107#10|10017002#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场17层3波</t>
-  </si>
-  <si>
-    <t>10017003#11#144#107#10|10017003#11#144#89#10|10017003#11#135#98#10|10017003#11#126#107#10|10017003#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场17层4波</t>
-  </si>
-  <si>
-    <t>10017004#11#144#107#10|10017004#11#144#89#10|10017004#11#135#98#10|10017004#11#126#107#10|10017004#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场18层1波</t>
-  </si>
-  <si>
-    <t>10018001#11#144#107#10|10018001#11#144#89#10|10018001#11#135#98#10|10018001#11#126#107#10|10018001#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场18层2波</t>
-  </si>
-  <si>
-    <t>10018002#11#144#107#10|10018002#11#144#89#10|10018002#11#135#98#10|10018002#11#126#107#10|10018002#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场18层3波</t>
-  </si>
-  <si>
-    <t>10018003#11#144#107#10|10018003#11#144#89#10|10018003#11#135#98#10|10018003#11#126#107#10|10018003#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场18层4波</t>
-  </si>
-  <si>
-    <t>10018004#11#144#107#10|10018004#11#144#89#10|10018004#11#135#98#10|10018004#11#126#107#10|10018004#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场19层1波</t>
-  </si>
-  <si>
-    <t>10019001#11#144#107#10|10019001#11#144#89#10|10019001#11#135#98#10|10019001#11#126#107#10|10019001#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场19层2波</t>
-  </si>
-  <si>
-    <t>10019002#11#144#107#10|10019002#11#144#89#10|10019002#11#135#98#10|10019002#11#126#107#10|10019002#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场19层3波</t>
-  </si>
-  <si>
-    <t>10019003#11#144#107#10|10019003#11#144#89#10|10019003#11#135#98#10|10019003#11#126#107#10|10019003#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场19层4波</t>
-  </si>
-  <si>
-    <t>10019004#11#144#107#10|10019004#11#144#89#10|10019004#11#135#98#10|10019004#11#126#107#10|10019004#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场20层1波</t>
-  </si>
-  <si>
-    <t>10020001#11#144#107#10|10020001#11#144#89#10|10020001#11#135#98#10|10020001#11#126#107#10|10020001#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场20层2波</t>
-  </si>
-  <si>
-    <t>10020002#11#144#107#10|10020002#11#144#89#10|10020002#11#135#98#10|10020002#11#126#107#10|10020002#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场20层3波</t>
-  </si>
-  <si>
-    <t>10020003#11#144#107#10|10020003#11#144#89#10|10020003#11#135#98#10|10020003#11#126#107#10|10020003#11#123#90#10</t>
-  </si>
-  <si>
-    <t>恶魔广场20层4波</t>
-  </si>
-  <si>
-    <t>10020004#11#144#107#10|10020004#11#144#89#10|10020004#11#135#98#10|10020004#11#126#107#10|10020004#11#123#90#10</t>
-  </si>
-  <si>
-    <t>血色城堡1</t>
-  </si>
-  <si>
-    <t>血色城堡2</t>
-  </si>
-  <si>
-    <t>血色城堡3</t>
-  </si>
-  <si>
-    <t>血色城堡4</t>
-  </si>
-  <si>
-    <t>血色城堡5</t>
-  </si>
-  <si>
-    <t>血色城堡6</t>
-  </si>
-  <si>
-    <t>血色城堡7</t>
-  </si>
-  <si>
-    <t>血色城堡8</t>
-  </si>
-  <si>
-    <t>血色城堡9</t>
-  </si>
-  <si>
-    <t>血色城堡10</t>
-  </si>
-  <si>
-    <t>血色城堡11</t>
-  </si>
-  <si>
-    <t>11011001#8#14#21#3|11011002#8#14#24#3|11011003#8#14#27#3|11011004#8#14#31#3|11011001#8#14#34#3|11011002#8#14#37#3|11011003#8#14#41#3|11011004#8#14#44#3|11011001#8#14#47#3|11011002#8#14#51#3|11011003#8#14#54#3|11011004#8#14#57#3|11011001#8#14#59#3|11011002#8#14#61#3|11011003#8#14#64#3|11011005#5#14#85#5|11011005#5#21#82#5|11011005#5#22#88#5|11011006#5#14#85#5|11011006#5#21#82#5|11011006#5#22#88#5</t>
-  </si>
-  <si>
-    <t>血色城堡12</t>
-  </si>
-  <si>
-    <t>11012001#8#14#21#3|11012002#8#14#24#3|11012003#8#14#27#3|11012004#8#14#31#3|11012001#8#14#34#3|11012002#8#14#37#3|11012003#8#14#41#3|11012004#8#14#44#3|11012001#8#14#47#3|11012002#8#14#51#3|11012003#8#14#54#3|11012004#8#14#57#3|11012001#8#14#59#3|11012002#8#14#61#3|11012003#8#14#64#3|11012005#5#14#85#5|11012005#5#21#82#5|11012005#5#22#88#5|11012006#5#14#85#5|11012006#5#21#82#5|11012006#5#22#88#5</t>
-  </si>
-  <si>
-    <t>血色城堡13</t>
-  </si>
-  <si>
-    <t>11013001#8#14#21#3|11013002#8#14#24#3|11013003#8#14#27#3|11013004#8#14#31#3|11013001#8#14#34#3|11013002#8#14#37#3|11013003#8#14#41#3|11013004#8#14#44#3|11013001#8#14#47#3|11013002#8#14#51#3|11013003#8#14#54#3|11013004#8#14#57#3|11013001#8#14#59#3|11013002#8#14#61#3|11013003#8#14#64#3|11013005#5#14#85#5|11013005#5#21#82#5|11013005#5#22#88#5|11013006#5#14#85#5|11013006#5#21#82#5|11013006#5#22#88#5</t>
-  </si>
-  <si>
-    <t>血色城堡14</t>
-  </si>
-  <si>
-    <t>11014001#8#14#21#3|11014002#8#14#24#3|11014003#8#14#27#3|11014004#8#14#31#3|11014001#8#14#34#3|11014002#8#14#37#3|11014003#8#14#41#3|11014004#8#14#44#3|11014001#8#14#47#3|11014002#8#14#51#3|11014003#8#14#54#3|11014004#8#14#57#3|11014001#8#14#59#3|11014002#8#14#61#3|11014003#8#14#64#3|11014005#5#14#85#5|11014005#5#21#82#5|11014005#5#22#88#5|11014006#5#14#85#5|11014006#5#21#82#5|11014006#5#22#88#5</t>
-  </si>
-  <si>
-    <t>血色城堡15</t>
-  </si>
-  <si>
-    <t>11015001#8#14#21#3|11015002#8#14#24#3|11015003#8#14#27#3|11015004#8#14#31#3|11015001#8#14#34#3|11015002#8#14#37#3|11015003#8#14#41#3|11015004#8#14#44#3|11015001#8#14#47#3|11015002#8#14#51#3|11015003#8#14#54#3|11015004#8#14#57#3|11015001#8#14#59#3|11015002#8#14#61#3|11015003#8#14#64#3|11015005#5#14#85#5|11015005#5#21#82#5|11015005#5#22#88#5|11015006#5#14#85#5|11015006#5#21#82#5|11015006#5#22#88#5</t>
-  </si>
-  <si>
-    <t>血色城堡16</t>
-  </si>
-  <si>
-    <t>11016001#8#14#21#3|11016002#8#14#24#3|11016003#8#14#27#3|11016004#8#14#31#3|11016001#8#14#34#3|11016002#8#14#37#3|11016003#8#14#41#3|11016004#8#14#44#3|11016001#8#14#47#3|11016002#8#14#51#3|11016003#8#14#54#3|11016004#8#14#57#3|11016001#8#14#59#3|11016002#8#14#61#3|11016003#8#14#64#3|11016005#5#14#85#5|11016005#5#21#82#5|11016005#5#22#88#5|11016006#5#14#85#5|11016006#5#21#82#5|11016006#5#22#88#5</t>
-  </si>
-  <si>
-    <t>血色城堡17</t>
-  </si>
-  <si>
-    <t>11017001#8#14#21#3|11017002#8#14#24#3|11017003#8#14#27#3|11017004#8#14#31#3|11017001#8#14#34#3|11017002#8#14#37#3|11017003#8#14#41#3|11017004#8#14#44#3|11017001#8#14#47#3|11017002#8#14#51#3|11017003#8#14#54#3|11017004#8#14#57#3|11017001#8#14#59#3|11017002#8#14#61#3|11017003#8#14#64#3|11017005#5#14#85#5|11017005#5#21#82#5|11017005#5#22#88#5|11017006#5#14#85#5|11017006#5#21#82#5|11017006#5#22#88#5</t>
-  </si>
-  <si>
-    <t>血色城堡18</t>
-  </si>
-  <si>
-    <t>11018001#8#14#21#3|11018002#8#14#24#3|11018003#8#14#27#3|11018004#8#14#31#3|11018001#8#14#34#3|11018002#8#14#37#3|11018003#8#14#41#3|11018004#8#14#44#3|11018001#8#14#47#3|11018002#8#14#51#3|11018003#8#14#54#3|11018004#8#14#57#3|11018001#8#14#59#3|11018002#8#14#61#3|11018003#8#14#64#3|11018005#5#14#85#5|11018005#5#21#82#5|11018005#5#22#88#5|11018006#5#14#85#5|11018006#5#21#82#5|11018006#5#22#88#5</t>
-  </si>
-  <si>
-    <t>血色城堡19</t>
-  </si>
-  <si>
-    <t>11019001#8#14#21#3|11019002#8#14#24#3|11019003#8#14#27#3|11019004#8#14#31#3|11019001#8#14#34#3|11019002#8#14#37#3|11019003#8#14#41#3|11019004#8#14#44#3|11019001#8#14#47#3|11019002#8#14#51#3|11019003#8#14#54#3|11019004#8#14#57#3|11019001#8#14#59#3|11019002#8#14#61#3|11019003#8#14#64#3|11019005#5#14#85#5|11019005#5#21#82#5|11019005#5#22#88#5|11019006#5#14#85#5|11019006#5#21#82#5|11019006#5#22#88#5</t>
-  </si>
-  <si>
-    <t>血色城堡20</t>
-  </si>
-  <si>
-    <t>11020001#8#14#21#3|11020002#8#14#24#3|11020003#8#14#27#3|11020004#8#14#31#3|11020001#8#14#34#3|11020002#8#14#37#3|11020003#8#14#41#3|11020004#8#14#44#3|11020001#8#14#47#3|11020002#8#14#51#3|11020003#8#14#54#3|11020004#8#14#57#3|11020001#8#14#59#3|11020002#8#14#61#3|11020003#8#14#64#3|11020005#5#14#85#5|11020005#5#21#82#5|11020005#5#22#88#5|11020006#5#14#85#5|11020006#5#21#82#5|11020006#5#22#88#5</t>
-  </si>
-  <si>
-    <t>勇气试炼1</t>
-  </si>
-  <si>
-    <t>26001#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼2</t>
-  </si>
-  <si>
-    <t>26002#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼3</t>
-  </si>
-  <si>
-    <t>26003#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼4</t>
-  </si>
-  <si>
-    <t>26004#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼5</t>
-  </si>
-  <si>
-    <t>26005#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼6</t>
-  </si>
-  <si>
-    <t>26006#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼7</t>
-  </si>
-  <si>
-    <t>26007#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼8</t>
-  </si>
-  <si>
-    <t>26008#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼9</t>
-  </si>
-  <si>
-    <t>26009#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼10</t>
-  </si>
-  <si>
-    <t>26010#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼11</t>
-  </si>
-  <si>
-    <t>26011#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼12</t>
-  </si>
-  <si>
-    <t>26012#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼13</t>
-  </si>
-  <si>
-    <t>26013#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼14</t>
-  </si>
-  <si>
-    <t>26014#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼15</t>
-  </si>
-  <si>
-    <t>26015#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼16</t>
-  </si>
-  <si>
-    <t>26016#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼17</t>
-  </si>
-  <si>
-    <t>26017#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼18</t>
-  </si>
-  <si>
-    <t>26018#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼19</t>
-  </si>
-  <si>
-    <t>26019#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼20</t>
-  </si>
-  <si>
-    <t>26020#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼21</t>
-  </si>
-  <si>
-    <t>26021#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼22</t>
-  </si>
-  <si>
-    <t>26022#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼23</t>
-  </si>
-  <si>
-    <t>26023#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼24</t>
-  </si>
-  <si>
-    <t>26024#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼25</t>
-  </si>
-  <si>
-    <t>26025#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼26</t>
-  </si>
-  <si>
-    <t>26026#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼27</t>
-  </si>
-  <si>
-    <t>26027#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼28</t>
-  </si>
-  <si>
-    <t>26028#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼29</t>
-  </si>
-  <si>
-    <t>26029#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼30</t>
-  </si>
-  <si>
-    <t>26030#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼31</t>
-  </si>
-  <si>
-    <t>26031#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼32</t>
-  </si>
-  <si>
-    <t>26032#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼33</t>
-  </si>
-  <si>
-    <t>26033#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼34</t>
-  </si>
-  <si>
-    <t>26034#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼35</t>
-  </si>
-  <si>
-    <t>26035#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼36</t>
-  </si>
-  <si>
-    <t>26036#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼37</t>
-  </si>
-  <si>
-    <t>26037#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼38</t>
-  </si>
-  <si>
-    <t>26038#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼39</t>
-  </si>
-  <si>
-    <t>26039#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼40</t>
-  </si>
-  <si>
-    <t>26040#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼41</t>
-  </si>
-  <si>
-    <t>26041#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼42</t>
-  </si>
-  <si>
-    <t>26042#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼43</t>
-  </si>
-  <si>
-    <t>26043#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼44</t>
-  </si>
-  <si>
-    <t>26044#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼45</t>
-  </si>
-  <si>
-    <t>26045#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼46</t>
-  </si>
-  <si>
-    <t>26046#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼47</t>
-  </si>
-  <si>
-    <t>26047#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼48</t>
-  </si>
-  <si>
-    <t>26048#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼49</t>
-  </si>
-  <si>
-    <t>26049#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼50</t>
-  </si>
-  <si>
-    <t>26050#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼51</t>
-  </si>
-  <si>
-    <t>26051#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼52</t>
-  </si>
-  <si>
-    <t>26052#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼53</t>
-  </si>
-  <si>
-    <t>26053#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼54</t>
-  </si>
-  <si>
-    <t>26054#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼55</t>
-  </si>
-  <si>
-    <t>26055#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼56</t>
-  </si>
-  <si>
-    <t>26056#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼57</t>
-  </si>
-  <si>
-    <t>26057#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼58</t>
-  </si>
-  <si>
-    <t>26058#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼59</t>
-  </si>
-  <si>
-    <t>26059#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼60</t>
-  </si>
-  <si>
-    <t>26060#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼61</t>
-  </si>
-  <si>
-    <t>26061#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼62</t>
-  </si>
-  <si>
-    <t>26062#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼63</t>
-  </si>
-  <si>
-    <t>26063#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼64</t>
-  </si>
-  <si>
-    <t>26064#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼65</t>
-  </si>
-  <si>
-    <t>26065#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼66</t>
-  </si>
-  <si>
-    <t>26066#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼67</t>
-  </si>
-  <si>
-    <t>26067#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼68</t>
-  </si>
-  <si>
-    <t>26068#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼69</t>
-  </si>
-  <si>
-    <t>26069#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼70</t>
-  </si>
-  <si>
-    <t>26070#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼71</t>
-  </si>
-  <si>
-    <t>26071#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼72</t>
-  </si>
-  <si>
-    <t>26072#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼73</t>
-  </si>
-  <si>
-    <t>26073#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼74</t>
-  </si>
-  <si>
-    <t>26074#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼75</t>
-  </si>
-  <si>
-    <t>26075#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼76</t>
-  </si>
-  <si>
-    <t>26076#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼77</t>
-  </si>
-  <si>
-    <t>26077#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼78</t>
-  </si>
-  <si>
-    <t>26078#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼79</t>
-  </si>
-  <si>
-    <t>26079#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼80</t>
-  </si>
-  <si>
-    <t>26080#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼81</t>
-  </si>
-  <si>
-    <t>26081#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼82</t>
-  </si>
-  <si>
-    <t>26082#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼83</t>
-  </si>
-  <si>
-    <t>26083#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼84</t>
-  </si>
-  <si>
-    <t>26084#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼85</t>
-  </si>
-  <si>
-    <t>26085#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼86</t>
-  </si>
-  <si>
-    <t>26086#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼87</t>
-  </si>
-  <si>
-    <t>26087#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼88</t>
-  </si>
-  <si>
-    <t>26088#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼89</t>
-  </si>
-  <si>
-    <t>26089#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼90</t>
-  </si>
-  <si>
-    <t>26090#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼91</t>
-  </si>
-  <si>
-    <t>26091#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼92</t>
-  </si>
-  <si>
-    <t>26092#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼93</t>
-  </si>
-  <si>
-    <t>26093#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼94</t>
-  </si>
-  <si>
-    <t>26094#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼95</t>
-  </si>
-  <si>
-    <t>26095#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼96</t>
-  </si>
-  <si>
-    <t>26096#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼97</t>
-  </si>
-  <si>
-    <t>26097#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼98</t>
-  </si>
-  <si>
-    <t>26098#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼99</t>
-  </si>
-  <si>
-    <t>26099#1#31#212#1</t>
-  </si>
-  <si>
-    <t>勇气试炼100</t>
-  </si>
-  <si>
-    <t>26100#1#31#212#1</t>
-  </si>
-  <si>
-    <t>15001001#3#65#36#1|15001001#3#180#33#1|15001001#3#120#75#1|15001001#3#167#23#1|15001001#3#195#48#1|15001001#3#98#82#1|15001001#3#84#57#1|15001001#3#174#45#1|15001001#3#150#103#1|15001001#3#159#85#1|15001001#3#114#96#1|15001001#3#42#72#1|15001001#3#205#75#1|15001001#3#86#96#1|15001001#3#22#121#1|15001002#2#65#36#1|15001002#2#180#33#1|15001002#2#120#75#1|15001002#2#167#23#1|15001002#2#195#48#1|15001002#2#98#82#1|15001002#2#84#57#1|15001002#2#174#45#1|15001002#2#150#103#1|15001002#2#159#85#1|15001002#2#114#96#1|15001002#2#42#72#1|15001002#2#205#75#1|15001002#2#86#96#1|15001002#2#22#121#1|15001003#1#65#36#1|15001003#1#180#33#1|15001003#1#120#75#1|15001003#1#167#23#1|15001003#1#195#48#1|15001003#1#98#82#1|15001003#1#84#57#1|15001003#1#174#45#1|15001003#1#150#103#1|15001003#1#159#85#1|15001003#1#114#96#1|15001003#1#42#72#1|15001003#1#205#75#1|15001003#1#86#96#1|15001003#1#22#121#1</t>
-  </si>
-  <si>
-    <t>15001004#3#65#36#1|15001004#3#180#33#1|15001004#3#120#75#1|15001004#3#167#23#1|15001004#3#195#48#1|15001004#3#98#82#1|15001004#3#84#57#1|15001004#3#174#45#1|15001004#3#150#103#1|15001004#3#159#85#1|15001004#3#114#96#1|15001004#3#42#72#1|15001004#3#205#75#1|15001004#3#86#96#1|15001005#2#65#36#1|15001005#2#180#33#1|15001005#2#120#75#1|15001005#2#167#23#1|15001005#2#195#48#1|15001005#2#98#82#1|15001005#2#84#57#1|15001005#2#174#45#1|15001005#2#150#103#1|15001005#2#159#85#1|15001005#2#114#96#1|15001005#2#42#72#1|15001005#2#205#75#1|15001005#2#86#96#1|15001006#1#65#36#1|15001006#1#180#33#1|15001006#1#120#75#1|15001006#1#167#23#1|15001006#1#195#48#1|15001006#1#98#82#1|15001006#1#84#57#1|15001006#1#174#45#1|15001006#1#150#103#1|15001006#1#159#85#1|15001006#1#114#96#1|15001006#1#42#72#1|15001006#1#205#75#1|15001006#1#86#96#1</t>
-  </si>
-  <si>
-    <t>15001007#3#65#36#1|15001007#3#180#33#1|15001007#3#120#75#1|15001007#3#167#23#1|15001007#3#195#48#1|15001007#3#98#82#1|15001007#3#84#57#1|15001007#3#174#45#1|15001007#3#150#103#1|15001007#3#159#85#1|15001007#3#114#96#1|15001007#3#42#72#1|15001007#3#205#75#1|15001008#2#65#36#1|15001008#2#180#33#1|15001008#2#120#75#1|15001008#2#167#23#1|15001008#2#195#48#1|15001008#2#98#82#1|15001008#2#84#57#1|15001008#2#174#45#1|15001008#2#150#103#1|15001008#2#159#85#1|15001008#2#114#96#1|15001008#2#42#72#1|15001008#2#205#75#1|15001009#1#65#36#1|15001009#1#180#33#1|15001009#1#120#75#1|15001009#1#167#23#1|15001009#1#195#48#1|15001009#1#98#82#1|15001009#1#84#57#1|15001009#1#174#45#1|15001009#1#150#103#1|15001009#1#159#85#1|15001009#1#114#96#1|15001009#1#42#72#1|15001009#1#205#75#1</t>
-  </si>
-  <si>
-    <t>15001010#3#65#36#1|15001010#3#180#33#1|15001010#3#120#75#1|15001010#3#167#23#1|15001010#3#195#48#1|15001010#3#98#82#1|15001010#3#84#57#1|15001010#3#174#45#1|15001010#3#150#103#1|15001010#3#159#85#1|15001010#3#114#96#1|15001010#3#42#72#1|15001011#2#65#36#1|15001011#2#180#33#1|15001011#2#120#75#1|15001011#2#167#23#1|15001011#2#195#48#1|15001011#2#98#82#1|15001011#2#84#57#1|15001011#2#174#45#1|15001011#2#150#103#1|15001011#2#159#85#1|15001011#2#114#96#1|15001011#2#42#72#1|15001012#1#65#36#1|15001012#1#180#33#1|15001012#1#120#75#1|15001012#1#167#23#1|15001012#1#195#48#1|15001012#1#98#82#1|15001012#1#84#57#1|15001012#1#174#45#1|15001012#1#150#103#1|15001012#1#159#85#1|15001012#1#114#96#1|15001012#1#42#72#1</t>
-  </si>
-  <si>
-    <t>15001013#3#65#36#1|15001013#3#180#33#1|15001013#3#120#75#1|15001013#3#167#23#1|15001013#3#195#48#1|15001013#3#98#82#1|15001013#3#84#57#1|15001013#3#174#45#1|15001013#3#150#103#1|15001013#3#159#85#1|15001013#3#114#96#1|15001014#2#65#36#1|15001014#2#180#33#1|15001014#2#120#75#1|15001014#2#167#23#1|15001014#2#195#48#1|15001014#2#98#82#1|15001014#2#84#57#1|15001014#2#174#45#1|15001014#2#150#103#1|15001014#2#159#85#1|15001014#2#114#96#1|15001015#1#65#36#1|15001015#1#180#33#1|15001015#1#120#75#1|15001015#1#167#23#1|15001015#1#195#48#1|15001015#1#98#82#1|15001015#1#84#57#1|15001015#1#174#45#1|15001015#1#150#103#1|15001015#1#159#85#1|15001015#1#114#96#1</t>
-  </si>
-  <si>
-    <t>15001016#3#65#36#1|15001016#3#180#33#1|15001016#3#120#75#1|15001016#3#167#23#1|15001016#3#195#48#1|15001016#3#98#82#1|15001016#3#84#57#1|15001016#3#174#45#1|15001016#3#150#103#1|15001016#3#159#85#1|15001017#2#65#36#1|15001017#2#180#33#1|15001017#2#120#75#1|15001017#2#167#23#1|15001017#2#195#48#1|15001017#2#98#82#1|15001017#2#84#57#1|15001017#2#174#45#1|15001017#2#150#103#1|15001017#2#159#85#1|15001018#1#65#36#1|15001018#1#180#33#1|15001018#1#120#75#1|15001018#1#167#23#1|15001018#1#195#48#1|15001018#1#98#82#1|15001018#1#84#57#1|15001018#1#174#45#1|15001018#1#150#103#1|15001018#1#159#85#1</t>
-  </si>
-  <si>
-    <t>15001019#3#65#36#1|15001019#3#180#33#1|15001019#3#120#75#1|15001019#3#167#23#1|15001019#3#195#48#1|15001019#3#98#82#1|15001019#3#84#57#1|15001019#3#174#45#1|15001019#3#150#103#1|15001020#2#65#36#1|15001020#2#180#33#1|15001020#2#120#75#1|15001020#2#167#23#1|15001020#2#195#48#1|15001020#2#98#82#1|15001020#2#84#57#1|15001020#2#174#45#1|15001020#2#150#103#1|15001021#1#65#36#1|15001021#1#180#33#1|15001021#1#120#75#1|15001021#1#167#23#1|15001021#1#195#48#1|15001021#1#98#82#1|15001021#1#84#57#1|15001021#1#174#45#1|15001021#1#150#103#1</t>
-  </si>
-  <si>
-    <t>15001022#3#65#36#1|15001022#3#180#33#1|15001022#3#120#75#1|15001022#3#167#23#1|15001022#3#195#48#1|15001022#3#98#82#1|15001022#3#84#57#1|15001022#3#174#45#1|15001022#3#150#103#1|15001023#2#65#36#1|15001023#2#180#33#1|15001023#2#120#75#1|15001023#2#167#23#1|15001023#2#195#48#1|15001023#2#98#82#1|15001023#2#84#57#1|15001023#2#174#45#1|15001023#2#150#103#1|15001024#1#65#36#1|15001024#1#180#33#1|15001024#1#120#75#1|15001024#1#167#23#1|15001024#1#195#48#1|15001024#1#98#82#1|15001024#1#84#57#1|15001024#1#174#45#1|15001024#1#150#103#1</t>
-  </si>
-  <si>
-    <t>15001025#3#65#36#1|15001025#3#180#33#1|15001025#3#120#75#1|15001025#3#167#23#1|15001025#3#195#48#1|15001025#3#98#82#1|15001025#3#84#57#1|15001025#3#174#45#1|15001025#3#150#103#1|15001026#2#65#36#1|15001026#2#180#33#1|15001026#2#120#75#1|15001026#2#167#23#1|15001026#2#195#48#1|15001026#2#98#82#1|15001026#2#84#57#1|15001026#2#174#45#1|15001026#2#150#103#1|15001027#1#65#36#1|15001027#1#180#33#1|15001027#1#120#75#1|15001027#1#167#23#1|15001027#1#195#48#1|15001027#1#98#82#1|15001027#1#84#57#1|15001027#1#174#45#1|15001027#1#150#103#1</t>
-  </si>
-  <si>
-    <t>15001028#3#65#36#1|15001028#3#180#33#1|15001028#3#120#75#1|15001028#3#167#23#1|15001028#3#195#48#1|15001028#3#98#82#1|15001028#3#84#57#1|15001028#3#174#45#1|15001028#3#150#103#1|15001029#2#65#36#1|15001029#2#180#33#1|15001029#2#120#75#1|15001029#2#167#23#1|15001029#2#195#48#1|15001029#2#98#82#1|15001029#2#84#57#1|15001029#2#174#45#1|15001029#2#150#103#1|15001030#1#65#36#1|15001030#1#180#33#1|15001030#1#120#75#1|15001030#1#167#23#1|15001030#1#195#48#1|15001030#1#98#82#1|15001030#1#84#57#1|15001030#1#174#45#1|15001030#1#150#103#1</t>
   </si>
   <si>
     <t>特权BOSS lv.50</t>
@@ -6570,7 +6570,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="81" s="2" customFormat="1" customHeight="1" spans="1:7">
+    <row r="81" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A81" s="5">
         <v>14001075</v>
       </c>
@@ -6584,7 +6584,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="82" s="2" customFormat="1" customHeight="1" spans="1:7">
+    <row r="82" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A82" s="5">
         <v>14001081</v>
       </c>
@@ -6602,7 +6602,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="83" s="2" customFormat="1" customHeight="1" spans="1:7">
+    <row r="83" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A83" s="5">
         <v>14001082</v>
       </c>
@@ -6620,7 +6620,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="84" s="2" customFormat="1" customHeight="1" spans="1:7">
+    <row r="84" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A84" s="5">
         <v>14001083</v>
       </c>
@@ -6638,7 +6638,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="85" s="2" customFormat="1" customHeight="1" spans="1:7">
+    <row r="85" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A85" s="5">
         <v>14001084</v>
       </c>
@@ -6656,7 +6656,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="86" s="2" customFormat="1" customHeight="1" spans="1:7">
+    <row r="86" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A86" s="5">
         <v>14001085</v>
       </c>
@@ -6670,7 +6670,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="87" s="2" customFormat="1" customHeight="1" spans="1:7">
+    <row r="87" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A87" s="5">
         <v>15001001</v>
       </c>
@@ -6687,16 +6687,13 @@
       <c r="F87" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="G87" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="88" s="2" customFormat="1" customHeight="1" spans="1:7">
+    </row>
+    <row r="88" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A88" s="5">
         <v>15001002</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C88" s="5">
         <v>15001003</v>
@@ -6708,16 +6705,13 @@
       <c r="F88" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="G88" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="89" s="2" customFormat="1" customHeight="1" spans="1:7">
+    </row>
+    <row r="89" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A89" s="5">
         <v>15001003</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C89" s="5">
         <v>15001004</v>
@@ -6727,18 +6721,15 @@
       </c>
       <c r="E89" s="5"/>
       <c r="F89" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="90" s="2" customFormat="1" customHeight="1" spans="1:7">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="90" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A90" s="5">
         <v>15001004</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C90" s="5">
         <v>15001005</v>
@@ -6748,18 +6739,15 @@
       </c>
       <c r="E90" s="5"/>
       <c r="F90" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="91" s="2" customFormat="1" customHeight="1" spans="1:7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="91" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A91" s="5">
         <v>15001005</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C91" s="5">
         <v>15001006</v>
@@ -6769,18 +6757,15 @@
       </c>
       <c r="E91" s="5"/>
       <c r="F91" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="92" s="2" customFormat="1" customHeight="1" spans="1:7">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="92" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A92" s="5">
         <v>15001006</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C92" s="5">
         <v>15001007</v>
@@ -6790,18 +6775,15 @@
       </c>
       <c r="E92" s="5"/>
       <c r="F92" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="93" s="2" customFormat="1" customHeight="1" spans="1:7">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="93" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A93" s="5">
         <v>15001007</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C93" s="5">
         <v>15001008</v>
@@ -6811,18 +6793,15 @@
       </c>
       <c r="E93" s="5"/>
       <c r="F93" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="94" s="2" customFormat="1" customHeight="1" spans="1:7">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="94" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A94" s="5">
         <v>15001008</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C94" s="5">
         <v>15001009</v>
@@ -6832,18 +6811,15 @@
       </c>
       <c r="E94" s="5"/>
       <c r="F94" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="95" s="2" customFormat="1" customHeight="1" spans="1:7">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="95" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A95" s="5">
         <v>15001009</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C95" s="5">
         <v>15001010</v>
@@ -6853,18 +6829,15 @@
       </c>
       <c r="E95" s="5"/>
       <c r="F95" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="96" s="2" customFormat="1" customHeight="1" spans="1:7">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="96" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A96" s="5">
         <v>15001010</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C96" s="5">
         <v>15001011</v>
@@ -6874,10 +6847,7 @@
       </c>
       <c r="E96" s="5"/>
       <c r="F96" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="97" s="2" customFormat="1" customHeight="1" spans="1:7">
@@ -6885,7 +6855,7 @@
         <v>15001011</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C97" s="5">
         <v>15001012</v>
@@ -6895,10 +6865,7 @@
       </c>
       <c r="E97" s="5"/>
       <c r="F97" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="98" s="2" customFormat="1" customHeight="1" spans="1:7">
@@ -6906,7 +6873,7 @@
         <v>15001012</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C98" s="5">
         <v>15001013</v>
@@ -6916,10 +6883,7 @@
       </c>
       <c r="E98" s="5"/>
       <c r="F98" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="99" s="2" customFormat="1" customHeight="1" spans="1:7">
@@ -6927,7 +6891,7 @@
         <v>15001013</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C99" s="5">
         <v>15001014</v>
@@ -6937,10 +6901,7 @@
       </c>
       <c r="E99" s="5"/>
       <c r="F99" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="100" s="2" customFormat="1" customHeight="1" spans="1:7">
@@ -6948,7 +6909,7 @@
         <v>15001014</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C100" s="5">
         <v>15001015</v>
@@ -6958,10 +6919,7 @@
       </c>
       <c r="E100" s="5"/>
       <c r="F100" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="101" s="2" customFormat="1" customHeight="1" spans="1:7">
@@ -6969,7 +6927,7 @@
         <v>15001015</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C101" s="5">
         <v>15001016</v>
@@ -6979,10 +6937,7 @@
       </c>
       <c r="E101" s="5"/>
       <c r="F101" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="102" s="2" customFormat="1" customHeight="1" spans="1:7">
@@ -6990,7 +6945,7 @@
         <v>15001016</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C102" s="5">
         <v>15001017</v>
@@ -7000,10 +6955,7 @@
       </c>
       <c r="E102" s="5"/>
       <c r="F102" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="103" s="2" customFormat="1" customHeight="1" spans="1:7">
@@ -7011,7 +6963,7 @@
         <v>15001017</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C103" s="5">
         <v>15001018</v>
@@ -7021,10 +6973,7 @@
       </c>
       <c r="E103" s="5"/>
       <c r="F103" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="104" s="2" customFormat="1" customHeight="1" spans="1:7">
@@ -7032,7 +6981,7 @@
         <v>15001018</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C104" s="5">
         <v>15001019</v>
@@ -7042,10 +6991,7 @@
       </c>
       <c r="E104" s="5"/>
       <c r="F104" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="105" s="2" customFormat="1" customHeight="1" spans="1:7">
@@ -7053,7 +6999,7 @@
         <v>15001019</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C105" s="5">
         <v>15001020</v>
@@ -7063,10 +7009,7 @@
       </c>
       <c r="E105" s="5"/>
       <c r="F105" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="106" s="2" customFormat="1" customHeight="1" spans="1:7">
@@ -7074,16 +7017,13 @@
         <v>15001020</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C106" s="5"/>
       <c r="D106" s="5"/>
       <c r="E106" s="5"/>
       <c r="F106" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="107" s="2" customFormat="1" customHeight="1" spans="1:7">
@@ -7091,13 +7031,13 @@
         <v>20001001</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C107" s="5"/>
       <c r="D107" s="5"/>
       <c r="E107" s="5"/>
       <c r="F107" s="5" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G107" s="5"/>
     </row>
@@ -7106,13 +7046,13 @@
         <v>20002001</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C108" s="5"/>
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G108" s="5"/>
     </row>
@@ -7121,13 +7061,13 @@
         <v>20003001</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C109" s="5"/>
       <c r="D109" s="5"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="G109" s="5"/>
     </row>
@@ -7136,13 +7076,13 @@
         <v>20004001</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C110" s="5"/>
       <c r="D110" s="5"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="G110" s="5"/>
     </row>
@@ -7151,13 +7091,13 @@
         <v>20005001</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C111" s="5"/>
       <c r="D111" s="5"/>
       <c r="E111" s="5"/>
       <c r="F111" s="5" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G111" s="5"/>
     </row>
@@ -7166,13 +7106,13 @@
         <v>20006001</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C112" s="5"/>
       <c r="D112" s="5"/>
       <c r="E112" s="5"/>
       <c r="F112" s="5" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G112" s="5"/>
     </row>
@@ -7181,13 +7121,13 @@
         <v>20007001</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C113" s="5"/>
       <c r="D113" s="5"/>
       <c r="E113" s="5"/>
       <c r="F113" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="G113" s="5"/>
     </row>
@@ -7358,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I5" s="1">
         <v>420</v>
@@ -7381,7 +7321,7 @@
         <v>300</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="I6" s="1">
         <v>540</v>
@@ -7404,7 +7344,7 @@
         <v>300</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="I7" s="1">
         <v>480</v>
@@ -7423,7 +7363,7 @@
         <v>300</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="I8" s="1">
         <v>480</v>
@@ -7446,7 +7386,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I9" s="1">
         <v>420</v>
@@ -7469,7 +7409,7 @@
         <v>300</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="I10" s="1">
         <v>540</v>
@@ -7492,7 +7432,7 @@
         <v>300</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="I11" s="1">
         <v>480</v>
@@ -7511,7 +7451,7 @@
         <v>300</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="I12" s="1">
         <v>480</v>
@@ -7534,7 +7474,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I13" s="1">
         <v>420</v>
@@ -7557,7 +7497,7 @@
         <v>300</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="I14" s="1">
         <v>540</v>
@@ -7580,7 +7520,7 @@
         <v>300</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="I15" s="1">
         <v>480</v>
@@ -7599,7 +7539,7 @@
         <v>300</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="I16" s="1">
         <v>480</v>
@@ -7622,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="I17" s="1">
         <v>420</v>
@@ -7645,7 +7585,7 @@
         <v>300</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="I18" s="1">
         <v>540</v>
@@ -7668,7 +7608,7 @@
         <v>300</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="I19" s="1">
         <v>480</v>
@@ -7687,7 +7627,7 @@
         <v>300</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="I20" s="1">
         <v>480</v>
@@ -7710,7 +7650,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="I21" s="1">
         <v>420</v>
@@ -7733,7 +7673,7 @@
         <v>300</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="I22" s="1">
         <v>540</v>
@@ -7756,7 +7696,7 @@
         <v>300</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="I23" s="1">
         <v>480</v>
@@ -7775,7 +7715,7 @@
         <v>300</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="I24" s="1">
         <v>480</v>
@@ -7798,7 +7738,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I25" s="1">
         <v>420</v>
@@ -7821,7 +7761,7 @@
         <v>300</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="I26" s="1">
         <v>540</v>
@@ -7844,7 +7784,7 @@
         <v>300</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="I27" s="1">
         <v>480</v>
@@ -7863,7 +7803,7 @@
         <v>300</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="I28" s="1">
         <v>480</v>
@@ -7886,7 +7826,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="I29" s="1">
         <v>420</v>
@@ -7909,7 +7849,7 @@
         <v>300</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="I30" s="1">
         <v>540</v>
@@ -7932,7 +7872,7 @@
         <v>300</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="I31" s="1">
         <v>480</v>
@@ -7951,7 +7891,7 @@
         <v>300</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="I32" s="1">
         <v>480</v>
@@ -7962,7 +7902,7 @@
         <v>10008001</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C33" s="5">
         <v>10008002</v>
@@ -7972,7 +7912,7 @@
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -7982,7 +7922,7 @@
         <v>10008002</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C34" s="5">
         <v>10008003</v>
@@ -7992,7 +7932,7 @@
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -8002,7 +7942,7 @@
         <v>10008003</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C35" s="5">
         <v>10008004</v>
@@ -8012,7 +7952,7 @@
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -8022,7 +7962,7 @@
         <v>10008004</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C36" s="5">
         <v>10008001</v>
@@ -8032,7 +7972,7 @@
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -8042,7 +7982,7 @@
         <v>10009001</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C37" s="5">
         <v>10009002</v>
@@ -8052,7 +7992,7 @@
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
@@ -8062,7 +8002,7 @@
         <v>10009002</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C38" s="5">
         <v>10009003</v>
@@ -8072,7 +8012,7 @@
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
@@ -8082,7 +8022,7 @@
         <v>10009003</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C39" s="5">
         <v>10009004</v>
@@ -8092,7 +8032,7 @@
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
@@ -8102,7 +8042,7 @@
         <v>10009004</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C40" s="5">
         <v>10009001</v>
@@ -8112,7 +8052,7 @@
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
@@ -8122,7 +8062,7 @@
         <v>10010001</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C41" s="5">
         <v>10010002</v>
@@ -8132,7 +8072,7 @@
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
@@ -8142,7 +8082,7 @@
         <v>10010002</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C42" s="5">
         <v>10010003</v>
@@ -8152,7 +8092,7 @@
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
@@ -8162,7 +8102,7 @@
         <v>10010003</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C43" s="5">
         <v>10010004</v>
@@ -8172,7 +8112,7 @@
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
@@ -8182,7 +8122,7 @@
         <v>10010004</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C44" s="5">
         <v>10010001</v>
@@ -8192,7 +8132,7 @@
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
@@ -8202,7 +8142,7 @@
         <v>10011001</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C45" s="5">
         <v>10011002</v>
@@ -8212,7 +8152,7 @@
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
@@ -8222,7 +8162,7 @@
         <v>10011002</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C46" s="5">
         <v>10011003</v>
@@ -8232,7 +8172,7 @@
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
@@ -8242,7 +8182,7 @@
         <v>10011003</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C47" s="5">
         <v>10011004</v>
@@ -8252,7 +8192,7 @@
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="H47" s="6"/>
       <c r="I47" s="6"/>
@@ -8262,7 +8202,7 @@
         <v>10011004</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C48" s="5">
         <v>10011001</v>
@@ -8272,7 +8212,7 @@
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
@@ -8282,7 +8222,7 @@
         <v>10012001</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C49" s="5">
         <v>10012002</v>
@@ -8292,7 +8232,7 @@
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="H49" s="6"/>
       <c r="I49" s="6"/>
@@ -8302,7 +8242,7 @@
         <v>10012002</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C50" s="5">
         <v>10012003</v>
@@ -8312,7 +8252,7 @@
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="H50" s="6"/>
       <c r="I50" s="6"/>
@@ -8322,7 +8262,7 @@
         <v>10012003</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C51" s="5">
         <v>10012004</v>
@@ -8332,7 +8272,7 @@
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="H51" s="6"/>
       <c r="I51" s="6"/>
@@ -8342,7 +8282,7 @@
         <v>10012004</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C52" s="5">
         <v>10012001</v>
@@ -8352,7 +8292,7 @@
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="H52" s="6"/>
       <c r="I52" s="6"/>
@@ -8362,7 +8302,7 @@
         <v>10013001</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C53" s="5">
         <v>10013002</v>
@@ -8372,7 +8312,7 @@
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="5" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="H53" s="6"/>
       <c r="I53" s="6"/>
@@ -8382,7 +8322,7 @@
         <v>10013002</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C54" s="5">
         <v>10013003</v>
@@ -8392,7 +8332,7 @@
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="5" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
@@ -8402,7 +8342,7 @@
         <v>10013003</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C55" s="5">
         <v>10013004</v>
@@ -8412,7 +8352,7 @@
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="5" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
@@ -8422,7 +8362,7 @@
         <v>10013004</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C56" s="5">
         <v>10013001</v>
@@ -8432,7 +8372,7 @@
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="H56" s="6"/>
       <c r="I56" s="6"/>
@@ -8442,7 +8382,7 @@
         <v>10014001</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C57" s="5">
         <v>10014002</v>
@@ -8452,7 +8392,7 @@
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="H57" s="6"/>
       <c r="I57" s="6"/>
@@ -8462,7 +8402,7 @@
         <v>10014002</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C58" s="5">
         <v>10014003</v>
@@ -8472,7 +8412,7 @@
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="5" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
@@ -8482,7 +8422,7 @@
         <v>10014003</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C59" s="5">
         <v>10014004</v>
@@ -8492,7 +8432,7 @@
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="H59" s="6"/>
       <c r="I59" s="6"/>
@@ -8502,7 +8442,7 @@
         <v>10014004</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C60" s="5">
         <v>10014001</v>
@@ -8512,7 +8452,7 @@
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="H60" s="6"/>
       <c r="I60" s="6"/>
@@ -8522,7 +8462,7 @@
         <v>10015001</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C61" s="5">
         <v>10015002</v>
@@ -8532,7 +8472,7 @@
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="5" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H61" s="6"/>
       <c r="I61" s="6"/>
@@ -8542,7 +8482,7 @@
         <v>10015002</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C62" s="5">
         <v>10015003</v>
@@ -8552,7 +8492,7 @@
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="5" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="H62" s="6"/>
       <c r="I62" s="6"/>
@@ -8562,7 +8502,7 @@
         <v>10015003</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C63" s="5">
         <v>10015004</v>
@@ -8572,7 +8512,7 @@
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="5" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
@@ -8582,7 +8522,7 @@
         <v>10015004</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C64" s="5">
         <v>10015001</v>
@@ -8592,7 +8532,7 @@
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="5" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
@@ -8602,7 +8542,7 @@
         <v>10016001</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C65" s="5">
         <v>10016002</v>
@@ -8612,7 +8552,7 @@
       </c>
       <c r="E65" s="5"/>
       <c r="F65" s="5" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
@@ -8622,7 +8562,7 @@
         <v>10016002</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C66" s="5">
         <v>10016003</v>
@@ -8632,7 +8572,7 @@
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="5" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
@@ -8642,7 +8582,7 @@
         <v>10016003</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C67" s="5">
         <v>10016004</v>
@@ -8652,7 +8592,7 @@
       </c>
       <c r="E67" s="5"/>
       <c r="F67" s="5" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
@@ -8662,7 +8602,7 @@
         <v>10016004</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C68" s="5">
         <v>10016001</v>
@@ -8672,7 +8612,7 @@
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
@@ -8682,7 +8622,7 @@
         <v>10017001</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C69" s="5">
         <v>10017002</v>
@@ -8692,7 +8632,7 @@
       </c>
       <c r="E69" s="5"/>
       <c r="F69" s="5" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
@@ -8702,7 +8642,7 @@
         <v>10017002</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C70" s="5">
         <v>10017003</v>
@@ -8712,7 +8652,7 @@
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="5" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
@@ -8722,7 +8662,7 @@
         <v>10017003</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C71" s="5">
         <v>10017004</v>
@@ -8732,7 +8672,7 @@
       </c>
       <c r="E71" s="5"/>
       <c r="F71" s="5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
@@ -8742,7 +8682,7 @@
         <v>10017004</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C72" s="5">
         <v>10017001</v>
@@ -8752,7 +8692,7 @@
       </c>
       <c r="E72" s="5"/>
       <c r="F72" s="5" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
@@ -8762,7 +8702,7 @@
         <v>10018001</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C73" s="5">
         <v>10018002</v>
@@ -8772,7 +8712,7 @@
       </c>
       <c r="E73" s="5"/>
       <c r="F73" s="5" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
@@ -8782,7 +8722,7 @@
         <v>10018002</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C74" s="5">
         <v>10018003</v>
@@ -8792,7 +8732,7 @@
       </c>
       <c r="E74" s="5"/>
       <c r="F74" s="5" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
@@ -8802,7 +8742,7 @@
         <v>10018003</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C75" s="5">
         <v>10018004</v>
@@ -8812,7 +8752,7 @@
       </c>
       <c r="E75" s="5"/>
       <c r="F75" s="5" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="H75" s="6"/>
       <c r="I75" s="6"/>
@@ -8822,7 +8762,7 @@
         <v>10018004</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C76" s="5">
         <v>10018001</v>
@@ -8832,7 +8772,7 @@
       </c>
       <c r="E76" s="5"/>
       <c r="F76" s="5" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="H76" s="6"/>
       <c r="I76" s="6"/>
@@ -8842,7 +8782,7 @@
         <v>10019001</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C77" s="5">
         <v>10019002</v>
@@ -8852,7 +8792,7 @@
       </c>
       <c r="E77" s="5"/>
       <c r="F77" s="5" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
@@ -8862,7 +8802,7 @@
         <v>10019002</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C78" s="5">
         <v>10019003</v>
@@ -8872,7 +8812,7 @@
       </c>
       <c r="E78" s="5"/>
       <c r="F78" s="5" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
@@ -8882,7 +8822,7 @@
         <v>10019003</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C79" s="5">
         <v>10019004</v>
@@ -8892,7 +8832,7 @@
       </c>
       <c r="E79" s="5"/>
       <c r="F79" s="5" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="H79" s="6"/>
       <c r="I79" s="6"/>
@@ -8902,7 +8842,7 @@
         <v>10019004</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C80" s="5">
         <v>10019001</v>
@@ -8912,7 +8852,7 @@
       </c>
       <c r="E80" s="5"/>
       <c r="F80" s="5" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H80" s="6"/>
       <c r="I80" s="6"/>
@@ -8922,7 +8862,7 @@
         <v>10020001</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C81" s="5">
         <v>10020002</v>
@@ -8932,7 +8872,7 @@
       </c>
       <c r="E81" s="5"/>
       <c r="F81" s="5" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H81" s="6"/>
       <c r="I81" s="6"/>
@@ -8942,7 +8882,7 @@
         <v>10020002</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C82" s="5">
         <v>10020003</v>
@@ -8952,7 +8892,7 @@
       </c>
       <c r="E82" s="5"/>
       <c r="F82" s="5" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="H82" s="6"/>
       <c r="I82" s="6"/>
@@ -8962,7 +8902,7 @@
         <v>10020003</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C83" s="5">
         <v>10020004</v>
@@ -8972,7 +8912,7 @@
       </c>
       <c r="E83" s="5"/>
       <c r="F83" s="5" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="H83" s="6"/>
       <c r="I83" s="6"/>
@@ -8982,7 +8922,7 @@
         <v>10020004</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C84" s="5">
         <v>10020001</v>
@@ -8992,7 +8932,7 @@
       </c>
       <c r="E84" s="5"/>
       <c r="F84" s="5" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="H84" s="6"/>
       <c r="I84" s="6"/>
@@ -9002,7 +8942,7 @@
         <v>11001001</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
@@ -9018,7 +8958,7 @@
         <v>11002001</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
@@ -9034,7 +8974,7 @@
         <v>11003001</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
@@ -9050,7 +8990,7 @@
         <v>11004001</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
@@ -9066,7 +9006,7 @@
         <v>11005001</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
@@ -9082,7 +9022,7 @@
         <v>11006001</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C90" s="5"/>
       <c r="D90" s="5"/>
@@ -9098,7 +9038,7 @@
         <v>11007001</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
@@ -9114,7 +9054,7 @@
         <v>11008001</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
@@ -9130,7 +9070,7 @@
         <v>11009001</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
@@ -9146,7 +9086,7 @@
         <v>11010001</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
@@ -9162,13 +9102,13 @@
         <v>11011001</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
       <c r="F95" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="H95" s="6"/>
       <c r="I95" s="6"/>
@@ -9178,13 +9118,13 @@
         <v>11012001</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C96" s="5"/>
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
       <c r="F96" s="2" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="H96" s="6"/>
       <c r="I96" s="6"/>
@@ -9194,13 +9134,13 @@
         <v>11013001</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C97" s="5"/>
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
       <c r="F97" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
@@ -9210,13 +9150,13 @@
         <v>11014001</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
       <c r="F98" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
@@ -9226,13 +9166,13 @@
         <v>11015001</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
       <c r="F99" s="2" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
@@ -9242,13 +9182,13 @@
         <v>11016001</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C100" s="5"/>
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
       <c r="F100" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
@@ -9258,13 +9198,13 @@
         <v>11017001</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
       <c r="F101" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H101" s="1"/>
       <c r="I101" s="1"/>
@@ -9274,13 +9214,13 @@
         <v>11018001</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C102" s="5"/>
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
       <c r="F102" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
@@ -9290,13 +9230,13 @@
         <v>11019001</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C103" s="5"/>
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
       <c r="F103" s="2" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
@@ -9306,13 +9246,13 @@
         <v>11020001</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C104" s="5"/>
       <c r="D104" s="5"/>
       <c r="E104" s="5"/>
       <c r="F104" s="2" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H104" s="1"/>
       <c r="I104" s="1"/>
@@ -9322,13 +9262,13 @@
         <v>12001001</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C105" s="5"/>
       <c r="D105" s="5"/>
       <c r="E105" s="5"/>
       <c r="F105" s="5" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="H105" s="1"/>
       <c r="I105" s="1"/>
@@ -9338,13 +9278,13 @@
         <v>12002001</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C106" s="5"/>
       <c r="D106" s="5"/>
       <c r="E106" s="5"/>
       <c r="F106" s="5" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H106" s="1"/>
       <c r="I106" s="1"/>
@@ -9354,13 +9294,13 @@
         <v>12003001</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C107" s="5"/>
       <c r="D107" s="5"/>
       <c r="E107" s="5"/>
       <c r="F107" s="5" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
@@ -9370,13 +9310,13 @@
         <v>12004001</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C108" s="5"/>
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
@@ -9386,13 +9326,13 @@
         <v>12005001</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C109" s="5"/>
       <c r="D109" s="5"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
@@ -9402,13 +9342,13 @@
         <v>12006001</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C110" s="5"/>
       <c r="D110" s="5"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
@@ -9418,13 +9358,13 @@
         <v>12007001</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C111" s="5"/>
       <c r="D111" s="5"/>
       <c r="E111" s="5"/>
       <c r="F111" s="5" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
@@ -9434,13 +9374,13 @@
         <v>12008001</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C112" s="5"/>
       <c r="D112" s="5"/>
       <c r="E112" s="5"/>
       <c r="F112" s="5" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="1"/>
@@ -9450,13 +9390,13 @@
         <v>12009001</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C113" s="5"/>
       <c r="D113" s="5"/>
       <c r="E113" s="5"/>
       <c r="F113" s="5" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
@@ -9466,13 +9406,13 @@
         <v>12010001</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C114" s="5"/>
       <c r="D114" s="5"/>
       <c r="E114" s="5"/>
       <c r="F114" s="5" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
@@ -9482,13 +9422,13 @@
         <v>12011001</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C115" s="5"/>
       <c r="D115" s="5"/>
       <c r="E115" s="5"/>
       <c r="F115" s="5" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
@@ -9498,13 +9438,13 @@
         <v>12012001</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C116" s="5"/>
       <c r="D116" s="5"/>
       <c r="E116" s="5"/>
       <c r="F116" s="5" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
@@ -9514,13 +9454,13 @@
         <v>12013001</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C117" s="5"/>
       <c r="D117" s="5"/>
       <c r="E117" s="5"/>
       <c r="F117" s="5" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
@@ -9530,13 +9470,13 @@
         <v>12014001</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C118" s="5"/>
       <c r="D118" s="5"/>
       <c r="E118" s="5"/>
       <c r="F118" s="5" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
@@ -9546,13 +9486,13 @@
         <v>12015001</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C119" s="5"/>
       <c r="D119" s="5"/>
       <c r="E119" s="5"/>
       <c r="F119" s="5" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
@@ -9562,13 +9502,13 @@
         <v>12016001</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C120" s="5"/>
       <c r="D120" s="5"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="H120" s="1"/>
       <c r="I120" s="1"/>
@@ -9578,13 +9518,13 @@
         <v>12017001</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C121" s="5"/>
       <c r="D121" s="5"/>
       <c r="E121" s="5"/>
       <c r="F121" s="5" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
@@ -9594,13 +9534,13 @@
         <v>12018001</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C122" s="5"/>
       <c r="D122" s="5"/>
       <c r="E122" s="5"/>
       <c r="F122" s="5" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
@@ -9610,13 +9550,13 @@
         <v>12019001</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C123" s="5"/>
       <c r="D123" s="5"/>
       <c r="E123" s="5"/>
       <c r="F123" s="5" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="H123" s="1"/>
       <c r="I123" s="1"/>
@@ -9626,13 +9566,13 @@
         <v>12020001</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C124" s="5"/>
       <c r="D124" s="5"/>
       <c r="E124" s="5"/>
       <c r="F124" s="5" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
@@ -9642,13 +9582,13 @@
         <v>12021001</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C125" s="5"/>
       <c r="D125" s="5"/>
       <c r="E125" s="5"/>
       <c r="F125" s="5" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="H125" s="1"/>
       <c r="I125" s="1"/>
@@ -9658,13 +9598,13 @@
         <v>12022001</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C126" s="5"/>
       <c r="D126" s="5"/>
       <c r="E126" s="5"/>
       <c r="F126" s="5" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
@@ -9674,13 +9614,13 @@
         <v>12023001</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C127" s="5"/>
       <c r="D127" s="5"/>
       <c r="E127" s="5"/>
       <c r="F127" s="5" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
@@ -9690,13 +9630,13 @@
         <v>12024001</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C128" s="5"/>
       <c r="D128" s="5"/>
       <c r="E128" s="5"/>
       <c r="F128" s="5" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
@@ -9706,13 +9646,13 @@
         <v>12025001</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C129" s="5"/>
       <c r="D129" s="5"/>
       <c r="E129" s="5"/>
       <c r="F129" s="5" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="H129" s="1"/>
       <c r="I129" s="1"/>
@@ -9722,13 +9662,13 @@
         <v>12026001</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C130" s="5"/>
       <c r="D130" s="5"/>
       <c r="E130" s="5"/>
       <c r="F130" s="5" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="H130" s="1"/>
       <c r="I130" s="1"/>
@@ -9738,13 +9678,13 @@
         <v>12027001</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C131" s="5"/>
       <c r="D131" s="5"/>
       <c r="E131" s="5"/>
       <c r="F131" s="5" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="H131" s="1"/>
       <c r="I131" s="1"/>
@@ -9754,13 +9694,13 @@
         <v>12028001</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C132" s="5"/>
       <c r="D132" s="5"/>
       <c r="E132" s="5"/>
       <c r="F132" s="5" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="H132" s="1"/>
       <c r="I132" s="1"/>
@@ -9770,13 +9710,13 @@
         <v>12029001</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C133" s="5"/>
       <c r="D133" s="5"/>
       <c r="E133" s="5"/>
       <c r="F133" s="5" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="H133" s="1"/>
       <c r="I133" s="1"/>
@@ -9786,13 +9726,13 @@
         <v>12030001</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C134" s="5"/>
       <c r="D134" s="5"/>
       <c r="E134" s="5"/>
       <c r="F134" s="5" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="H134" s="1"/>
       <c r="I134" s="1"/>
@@ -9802,13 +9742,13 @@
         <v>12031001</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C135" s="5"/>
       <c r="D135" s="5"/>
       <c r="E135" s="5"/>
       <c r="F135" s="5" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="H135" s="1"/>
       <c r="I135" s="1"/>
@@ -9818,13 +9758,13 @@
         <v>12032001</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C136" s="5"/>
       <c r="D136" s="5"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="H136" s="1"/>
       <c r="I136" s="1"/>
@@ -9834,13 +9774,13 @@
         <v>12033001</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C137" s="5"/>
       <c r="D137" s="5"/>
       <c r="E137" s="5"/>
       <c r="F137" s="5" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
@@ -9850,13 +9790,13 @@
         <v>12034001</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C138" s="5"/>
       <c r="D138" s="5"/>
       <c r="E138" s="5"/>
       <c r="F138" s="5" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="H138" s="1"/>
       <c r="I138" s="1"/>
@@ -9866,13 +9806,13 @@
         <v>12035001</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C139" s="5"/>
       <c r="D139" s="5"/>
       <c r="E139" s="5"/>
       <c r="F139" s="5" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="H139" s="1"/>
       <c r="I139" s="1"/>
@@ -9882,13 +9822,13 @@
         <v>12036001</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C140" s="5"/>
       <c r="D140" s="5"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
@@ -9898,13 +9838,13 @@
         <v>12037001</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C141" s="5"/>
       <c r="D141" s="5"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="H141" s="1"/>
       <c r="I141" s="1"/>
@@ -9914,13 +9854,13 @@
         <v>12038001</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C142" s="5"/>
       <c r="D142" s="5"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="H142" s="1"/>
       <c r="I142" s="1"/>
@@ -9930,13 +9870,13 @@
         <v>12039001</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C143" s="5"/>
       <c r="D143" s="5"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="H143" s="1"/>
       <c r="I143" s="1"/>
@@ -9946,13 +9886,13 @@
         <v>12040001</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C144" s="5"/>
       <c r="D144" s="5"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="H144" s="1"/>
       <c r="I144" s="1"/>
@@ -9962,13 +9902,13 @@
         <v>12041001</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C145" s="5"/>
       <c r="D145" s="5"/>
       <c r="E145" s="5"/>
       <c r="F145" s="5" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="H145" s="1"/>
       <c r="I145" s="1"/>
@@ -9978,13 +9918,13 @@
         <v>12042001</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C146" s="5"/>
       <c r="D146" s="5"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="H146" s="1"/>
       <c r="I146" s="1"/>
@@ -9994,13 +9934,13 @@
         <v>12043001</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C147" s="5"/>
       <c r="D147" s="5"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="H147" s="1"/>
       <c r="I147" s="1"/>
@@ -10010,13 +9950,13 @@
         <v>12044001</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C148" s="5"/>
       <c r="D148" s="5"/>
       <c r="E148" s="5"/>
       <c r="F148" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="H148" s="1"/>
       <c r="I148" s="1"/>
@@ -10026,13 +9966,13 @@
         <v>12045001</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="C149" s="5"/>
       <c r="D149" s="5"/>
       <c r="E149" s="5"/>
       <c r="F149" s="5" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="H149" s="1"/>
       <c r="I149" s="1"/>
@@ -10042,13 +9982,13 @@
         <v>12046001</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C150" s="5"/>
       <c r="D150" s="5"/>
       <c r="E150" s="5"/>
       <c r="F150" s="5" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="H150" s="1"/>
       <c r="I150" s="1"/>
@@ -10058,13 +9998,13 @@
         <v>12047001</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="C151" s="5"/>
       <c r="D151" s="5"/>
       <c r="E151" s="5"/>
       <c r="F151" s="5" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="H151" s="1"/>
       <c r="I151" s="1"/>
@@ -10074,13 +10014,13 @@
         <v>12048001</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C152" s="5"/>
       <c r="D152" s="5"/>
       <c r="E152" s="5"/>
       <c r="F152" s="5" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="H152" s="1"/>
       <c r="I152" s="1"/>
@@ -10090,13 +10030,13 @@
         <v>12049001</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C153" s="5"/>
       <c r="D153" s="5"/>
       <c r="E153" s="5"/>
       <c r="F153" s="5" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
@@ -10106,13 +10046,13 @@
         <v>12050001</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C154" s="5"/>
       <c r="D154" s="5"/>
       <c r="E154" s="5"/>
       <c r="F154" s="5" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="H154" s="1"/>
       <c r="I154" s="1"/>
@@ -10122,13 +10062,13 @@
         <v>12051001</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C155" s="5"/>
       <c r="D155" s="5"/>
       <c r="E155" s="5"/>
       <c r="F155" s="5" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="H155" s="1"/>
       <c r="I155" s="1"/>
@@ -10138,13 +10078,13 @@
         <v>12052001</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C156" s="5"/>
       <c r="D156" s="5"/>
       <c r="E156" s="5"/>
       <c r="F156" s="5" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="H156" s="1"/>
       <c r="I156" s="1"/>
@@ -10154,13 +10094,13 @@
         <v>12053001</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C157" s="5"/>
       <c r="D157" s="5"/>
       <c r="E157" s="5"/>
       <c r="F157" s="5" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H157" s="1"/>
       <c r="I157" s="1"/>
@@ -10170,13 +10110,13 @@
         <v>12054001</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C158" s="5"/>
       <c r="D158" s="5"/>
       <c r="E158" s="5"/>
       <c r="F158" s="5" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H158" s="1"/>
       <c r="I158" s="1"/>
@@ -10186,13 +10126,13 @@
         <v>12055001</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C159" s="5"/>
       <c r="D159" s="5"/>
       <c r="E159" s="5"/>
       <c r="F159" s="5" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="H159" s="1"/>
       <c r="I159" s="1"/>
@@ -10202,13 +10142,13 @@
         <v>12056001</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C160" s="5"/>
       <c r="D160" s="5"/>
       <c r="E160" s="5"/>
       <c r="F160" s="5" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="H160" s="1"/>
       <c r="I160" s="1"/>
@@ -10218,13 +10158,13 @@
         <v>12057001</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C161" s="5"/>
       <c r="D161" s="5"/>
       <c r="E161" s="5"/>
       <c r="F161" s="5" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="H161" s="1"/>
       <c r="I161" s="1"/>
@@ -10234,13 +10174,13 @@
         <v>12058001</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C162" s="5"/>
       <c r="D162" s="5"/>
       <c r="E162" s="5"/>
       <c r="F162" s="5" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="H162" s="1"/>
       <c r="I162" s="1"/>
@@ -10250,13 +10190,13 @@
         <v>12059001</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C163" s="5"/>
       <c r="D163" s="5"/>
       <c r="E163" s="5"/>
       <c r="F163" s="5" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="H163" s="1"/>
       <c r="I163" s="1"/>
@@ -10266,13 +10206,13 @@
         <v>12060001</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="C164" s="5"/>
       <c r="D164" s="5"/>
       <c r="E164" s="5"/>
       <c r="F164" s="5" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="H164" s="1"/>
       <c r="I164" s="1"/>
@@ -10282,13 +10222,13 @@
         <v>12061001</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C165" s="5"/>
       <c r="D165" s="5"/>
       <c r="E165" s="5"/>
       <c r="F165" s="5" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="H165" s="1"/>
       <c r="I165" s="1"/>
@@ -10298,13 +10238,13 @@
         <v>12062001</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C166" s="5"/>
       <c r="D166" s="5"/>
       <c r="E166" s="5"/>
       <c r="F166" s="5" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="H166" s="1"/>
       <c r="I166" s="1"/>
@@ -10314,13 +10254,13 @@
         <v>12063001</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C167" s="5"/>
       <c r="D167" s="5"/>
       <c r="E167" s="5"/>
       <c r="F167" s="5" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="H167" s="1"/>
       <c r="I167" s="1"/>
@@ -10330,13 +10270,13 @@
         <v>12064001</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="C168" s="5"/>
       <c r="D168" s="5"/>
       <c r="E168" s="5"/>
       <c r="F168" s="5" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="H168" s="1"/>
       <c r="I168" s="1"/>
@@ -10346,13 +10286,13 @@
         <v>12065001</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C169" s="5"/>
       <c r="D169" s="5"/>
       <c r="E169" s="5"/>
       <c r="F169" s="5" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="H169" s="1"/>
       <c r="I169" s="1"/>
@@ -10362,13 +10302,13 @@
         <v>12066001</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="C170" s="5"/>
       <c r="D170" s="5"/>
       <c r="E170" s="5"/>
       <c r="F170" s="5" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="H170" s="1"/>
       <c r="I170" s="1"/>
@@ -10378,13 +10318,13 @@
         <v>12067001</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C171" s="5"/>
       <c r="D171" s="5"/>
       <c r="E171" s="5"/>
       <c r="F171" s="5" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="H171" s="1"/>
       <c r="I171" s="1"/>
@@ -10394,13 +10334,13 @@
         <v>12068001</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="C172" s="5"/>
       <c r="D172" s="5"/>
       <c r="E172" s="5"/>
       <c r="F172" s="5" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="H172" s="1"/>
       <c r="I172" s="1"/>
@@ -10410,13 +10350,13 @@
         <v>12069001</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="C173" s="5"/>
       <c r="D173" s="5"/>
       <c r="E173" s="5"/>
       <c r="F173" s="5" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="H173" s="1"/>
       <c r="I173" s="1"/>
@@ -10426,13 +10366,13 @@
         <v>12070001</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="C174" s="5"/>
       <c r="D174" s="5"/>
       <c r="E174" s="5"/>
       <c r="F174" s="5" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="H174" s="1"/>
       <c r="I174" s="1"/>
@@ -10442,13 +10382,13 @@
         <v>12071001</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="C175" s="5"/>
       <c r="D175" s="5"/>
       <c r="E175" s="5"/>
       <c r="F175" s="5" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="H175" s="1"/>
       <c r="I175" s="1"/>
@@ -10458,13 +10398,13 @@
         <v>12072001</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="C176" s="5"/>
       <c r="D176" s="5"/>
       <c r="E176" s="5"/>
       <c r="F176" s="5" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
@@ -10474,13 +10414,13 @@
         <v>12073001</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="C177" s="5"/>
       <c r="D177" s="5"/>
       <c r="E177" s="5"/>
       <c r="F177" s="5" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="H177" s="1"/>
       <c r="I177" s="1"/>
@@ -10490,13 +10430,13 @@
         <v>12074001</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="C178" s="5"/>
       <c r="D178" s="5"/>
       <c r="E178" s="5"/>
       <c r="F178" s="5" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="H178" s="1"/>
       <c r="I178" s="1"/>
@@ -10506,13 +10446,13 @@
         <v>12075001</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C179" s="5"/>
       <c r="D179" s="5"/>
       <c r="E179" s="5"/>
       <c r="F179" s="5" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="H179" s="1"/>
       <c r="I179" s="1"/>
@@ -10522,13 +10462,13 @@
         <v>12076001</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="C180" s="5"/>
       <c r="D180" s="5"/>
       <c r="E180" s="5"/>
       <c r="F180" s="5" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
@@ -10538,13 +10478,13 @@
         <v>12077001</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="C181" s="5"/>
       <c r="D181" s="5"/>
       <c r="E181" s="5"/>
       <c r="F181" s="5" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="H181" s="1"/>
       <c r="I181" s="1"/>
@@ -10554,13 +10494,13 @@
         <v>12078001</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="C182" s="5"/>
       <c r="D182" s="5"/>
       <c r="E182" s="5"/>
       <c r="F182" s="5" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="H182" s="1"/>
       <c r="I182" s="1"/>
@@ -10570,13 +10510,13 @@
         <v>12079001</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="C183" s="5"/>
       <c r="D183" s="5"/>
       <c r="E183" s="5"/>
       <c r="F183" s="5" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="H183" s="1"/>
       <c r="I183" s="1"/>
@@ -10586,13 +10526,13 @@
         <v>12080001</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="C184" s="5"/>
       <c r="D184" s="5"/>
       <c r="E184" s="5"/>
       <c r="F184" s="5" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="H184" s="1"/>
       <c r="I184" s="1"/>
@@ -10602,13 +10542,13 @@
         <v>12081001</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="C185" s="5"/>
       <c r="D185" s="5"/>
       <c r="E185" s="5"/>
       <c r="F185" s="5" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="H185" s="1"/>
       <c r="I185" s="1"/>
@@ -10618,13 +10558,13 @@
         <v>12082001</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="C186" s="5"/>
       <c r="D186" s="5"/>
       <c r="E186" s="5"/>
       <c r="F186" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="H186" s="1"/>
       <c r="I186" s="1"/>
@@ -10634,13 +10574,13 @@
         <v>12083001</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C187" s="5"/>
       <c r="D187" s="5"/>
       <c r="E187" s="5"/>
       <c r="F187" s="5" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="H187" s="1"/>
       <c r="I187" s="1"/>
@@ -10650,13 +10590,13 @@
         <v>12084001</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="C188" s="5"/>
       <c r="D188" s="5"/>
       <c r="E188" s="5"/>
       <c r="F188" s="5" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="H188" s="1"/>
       <c r="I188" s="1"/>
@@ -10666,13 +10606,13 @@
         <v>12085001</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C189" s="5"/>
       <c r="D189" s="5"/>
       <c r="E189" s="5"/>
       <c r="F189" s="5" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="H189" s="1"/>
       <c r="I189" s="1"/>
@@ -10682,13 +10622,13 @@
         <v>12086001</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="C190" s="5"/>
       <c r="D190" s="5"/>
       <c r="E190" s="5"/>
       <c r="F190" s="5" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="H190" s="1"/>
       <c r="I190" s="1"/>
@@ -10698,13 +10638,13 @@
         <v>12087001</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C191" s="5"/>
       <c r="D191" s="5"/>
       <c r="E191" s="5"/>
       <c r="F191" s="5" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="H191" s="1"/>
       <c r="I191" s="1"/>
@@ -10714,13 +10654,13 @@
         <v>12088001</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C192" s="5"/>
       <c r="D192" s="5"/>
       <c r="E192" s="5"/>
       <c r="F192" s="5" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="H192" s="1"/>
       <c r="I192" s="1"/>
@@ -10730,13 +10670,13 @@
         <v>12089001</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="C193" s="5"/>
       <c r="D193" s="5"/>
       <c r="E193" s="5"/>
       <c r="F193" s="5" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="H193" s="1"/>
       <c r="I193" s="1"/>
@@ -10746,13 +10686,13 @@
         <v>12090001</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="C194" s="5"/>
       <c r="D194" s="5"/>
       <c r="E194" s="5"/>
       <c r="F194" s="5" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="H194" s="1"/>
       <c r="I194" s="1"/>
@@ -10762,13 +10702,13 @@
         <v>12091001</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C195" s="5"/>
       <c r="D195" s="5"/>
       <c r="E195" s="5"/>
       <c r="F195" s="5" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="H195" s="1"/>
       <c r="I195" s="1"/>
@@ -10778,13 +10718,13 @@
         <v>12092001</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C196" s="5"/>
       <c r="D196" s="5"/>
       <c r="E196" s="5"/>
       <c r="F196" s="5" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="H196" s="1"/>
       <c r="I196" s="1"/>
@@ -10794,13 +10734,13 @@
         <v>12093001</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C197" s="5"/>
       <c r="D197" s="5"/>
       <c r="E197" s="5"/>
       <c r="F197" s="5" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="H197" s="1"/>
       <c r="I197" s="1"/>
@@ -10810,13 +10750,13 @@
         <v>12094001</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="C198" s="5"/>
       <c r="D198" s="5"/>
       <c r="E198" s="5"/>
       <c r="F198" s="5" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="H198" s="1"/>
       <c r="I198" s="1"/>
@@ -10826,13 +10766,13 @@
         <v>12095001</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C199" s="5"/>
       <c r="D199" s="5"/>
       <c r="E199" s="5"/>
       <c r="F199" s="5" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="H199" s="1"/>
       <c r="I199" s="1"/>
@@ -10842,13 +10782,13 @@
         <v>12096001</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="C200" s="5"/>
       <c r="D200" s="5"/>
       <c r="E200" s="5"/>
       <c r="F200" s="5" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="H200" s="1"/>
       <c r="I200" s="1"/>
@@ -10858,13 +10798,13 @@
         <v>12097001</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C201" s="5"/>
       <c r="D201" s="5"/>
       <c r="E201" s="5"/>
       <c r="F201" s="5" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="H201" s="1"/>
       <c r="I201" s="1"/>
@@ -10874,13 +10814,13 @@
         <v>12098001</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C202" s="5"/>
       <c r="D202" s="5"/>
       <c r="E202" s="5"/>
       <c r="F202" s="5" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="H202" s="1"/>
       <c r="I202" s="1"/>
@@ -10890,13 +10830,13 @@
         <v>12099001</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="C203" s="5"/>
       <c r="D203" s="5"/>
       <c r="E203" s="5"/>
       <c r="F203" s="5" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="H203" s="1"/>
       <c r="I203" s="1"/>
@@ -10906,13 +10846,13 @@
         <v>12100001</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C204" s="5"/>
       <c r="D204" s="5"/>
       <c r="E204" s="5"/>
       <c r="F204" s="5" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="H204" s="1"/>
       <c r="I204" s="1"/>
@@ -11700,10 +11640,10 @@
         <v>60</v>
       </c>
       <c r="F245" s="5" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>196</v>
+        <v>603</v>
       </c>
       <c r="H245" s="1"/>
       <c r="I245" s="1"/>
@@ -11713,7 +11653,7 @@
         <v>15001002</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C246" s="5">
         <v>15001003</v>
@@ -11723,10 +11663,10 @@
         <v>60</v>
       </c>
       <c r="F246" s="5" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>196</v>
+        <v>603</v>
       </c>
       <c r="H246" s="1"/>
       <c r="I246" s="1"/>
@@ -11736,7 +11676,7 @@
         <v>15001003</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C247" s="5">
         <v>15001004</v>
@@ -11746,10 +11686,10 @@
         <v>60</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>196</v>
+        <v>603</v>
       </c>
       <c r="H247" s="1"/>
       <c r="I247" s="1"/>
@@ -11759,7 +11699,7 @@
         <v>15001004</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C248" s="5">
         <v>15001005</v>
@@ -11769,10 +11709,10 @@
         <v>60</v>
       </c>
       <c r="F248" s="5" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>196</v>
+        <v>603</v>
       </c>
       <c r="H248" s="1"/>
       <c r="I248" s="1"/>
@@ -11782,7 +11722,7 @@
         <v>15001005</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C249" s="5">
         <v>15001006</v>
@@ -11792,10 +11732,10 @@
         <v>60</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>204</v>
+        <v>606</v>
       </c>
       <c r="H249" s="1"/>
       <c r="I249" s="1"/>
@@ -11805,7 +11745,7 @@
         <v>15001006</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C250" s="5">
         <v>15001007</v>
@@ -11815,10 +11755,10 @@
         <v>60</v>
       </c>
       <c r="F250" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>204</v>
+        <v>606</v>
       </c>
       <c r="H250" s="1"/>
       <c r="I250" s="1"/>
@@ -11828,7 +11768,7 @@
         <v>15001007</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C251" s="5">
         <v>15001008</v>
@@ -11838,10 +11778,10 @@
         <v>60</v>
       </c>
       <c r="F251" s="5" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>204</v>
+        <v>606</v>
       </c>
       <c r="H251" s="1"/>
       <c r="I251" s="1"/>
@@ -11851,7 +11791,7 @@
         <v>15001008</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C252" s="5">
         <v>15001009</v>
@@ -11861,10 +11801,10 @@
         <v>60</v>
       </c>
       <c r="F252" s="5" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>204</v>
+        <v>606</v>
       </c>
       <c r="H252" s="1"/>
       <c r="I252" s="1"/>
@@ -11874,7 +11814,7 @@
         <v>15001009</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C253" s="5">
         <v>15001010</v>
@@ -11884,10 +11824,10 @@
         <v>60</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>204</v>
+        <v>606</v>
       </c>
       <c r="H253" s="1"/>
       <c r="I253" s="1"/>
@@ -11897,7 +11837,7 @@
         <v>15001010</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C254" s="5">
         <v>15001011</v>
@@ -11907,10 +11847,10 @@
         <v>60</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>213</v>
+        <v>609</v>
       </c>
       <c r="H254" s="1"/>
       <c r="I254" s="1"/>
@@ -11920,7 +11860,7 @@
         <v>15001011</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C255" s="5">
         <v>15001012</v>
@@ -11930,10 +11870,10 @@
         <v>60</v>
       </c>
       <c r="F255" s="5" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>213</v>
+        <v>609</v>
       </c>
       <c r="H255" s="1"/>
       <c r="I255" s="1"/>
@@ -11943,7 +11883,7 @@
         <v>15001012</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C256" s="5">
         <v>15001013</v>
@@ -11953,10 +11893,10 @@
         <v>60</v>
       </c>
       <c r="F256" s="5" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>213</v>
+        <v>609</v>
       </c>
       <c r="H256" s="1"/>
       <c r="I256" s="1"/>
@@ -11966,7 +11906,7 @@
         <v>15001013</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C257" s="5">
         <v>15001014</v>
@@ -11976,10 +11916,10 @@
         <v>60</v>
       </c>
       <c r="F257" s="5" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>213</v>
+        <v>609</v>
       </c>
       <c r="H257" s="1"/>
       <c r="I257" s="1"/>
@@ -11989,7 +11929,7 @@
         <v>15001014</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C258" s="5">
         <v>15001015</v>
@@ -11999,10 +11939,10 @@
         <v>60</v>
       </c>
       <c r="F258" s="5" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>213</v>
+        <v>609</v>
       </c>
       <c r="H258" s="1"/>
       <c r="I258" s="1"/>
@@ -12012,7 +11952,7 @@
         <v>15001015</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C259" s="5">
         <v>15001016</v>
@@ -12022,10 +11962,10 @@
         <v>60</v>
       </c>
       <c r="F259" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>213</v>
+        <v>609</v>
       </c>
       <c r="H259" s="1"/>
       <c r="I259" s="1"/>
@@ -12035,7 +11975,7 @@
         <v>15001016</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C260" s="5">
         <v>15001017</v>
@@ -12045,10 +11985,10 @@
         <v>60</v>
       </c>
       <c r="F260" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>225</v>
+        <v>613</v>
       </c>
       <c r="H260" s="1"/>
       <c r="I260" s="1"/>
@@ -12058,7 +11998,7 @@
         <v>15001017</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C261" s="5">
         <v>15001018</v>
@@ -12068,10 +12008,10 @@
         <v>60</v>
       </c>
       <c r="F261" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>225</v>
+        <v>613</v>
       </c>
       <c r="H261" s="1"/>
       <c r="I261" s="1"/>
@@ -12081,7 +12021,7 @@
         <v>15001018</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C262" s="5">
         <v>15001019</v>
@@ -12091,10 +12031,10 @@
         <v>60</v>
       </c>
       <c r="F262" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>225</v>
+        <v>613</v>
       </c>
       <c r="H262" s="1"/>
       <c r="I262" s="1"/>
@@ -12104,7 +12044,7 @@
         <v>15001019</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C263" s="5">
         <v>15001020</v>
@@ -12114,10 +12054,10 @@
         <v>60</v>
       </c>
       <c r="F263" s="5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>225</v>
+        <v>613</v>
       </c>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
@@ -12127,7 +12067,7 @@
         <v>15001020</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C264" s="5"/>
       <c r="D264" s="5"/>
@@ -12135,10 +12075,10 @@
         <v>60</v>
       </c>
       <c r="F264" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="G264" s="2" t="s">
         <v>616</v>
-      </c>
-      <c r="G264" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
